--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,24 +49,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -159,15 +141,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,11 +760,11 @@
       <c r="E4" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>23</v>
+      <c r="F4" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>17</v>
@@ -800,48 +773,52 @@
         <v>6.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="n"/>
+      <c r="L4" s="3" t="n">
+        <v>16.1</v>
+      </c>
       <c r="M4" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N4" s="3" t="n"/>
+      <c r="N4" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="O4" s="3" t="n">
-        <v>84</v>
+        <v>845</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q4" s="8" t="n">
-        <v>227.8</v>
+      <c r="Q4" s="3" t="n">
+        <v>117.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>651.3</v>
+      <c r="S4" s="3" t="n">
+        <v>24.5</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>54.8</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V4" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V4" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>17.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>56.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>13.6</v>
@@ -861,7 +838,7 @@
       </c>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n">
-        <v>28.4</v>
+        <v>8.4</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>17.6</v>
@@ -870,7 +847,7 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>16.8</v>
@@ -882,52 +859,52 @@
         <v>9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>16.9</v>
+        <v>11.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>823.5</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q5" s="8" t="n">
-        <v>28.4</v>
+        <v>3.9</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>48.4</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>21.8</v>
+      <c r="S5" s="8" t="n">
+        <v>41.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U5" s="8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>18.2</v>
+        <v>1.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -949,17 +926,17 @@
       <c r="E6" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="9" t="n">
-        <v>92.8</v>
+      <c r="F6" s="8" t="n">
+        <v>32.1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>17.6</v>
+        <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>12.6</v>
@@ -967,9 +944,11 @@
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n"/>
+      <c r="L6" s="3" t="n">
+        <v>18.6</v>
+      </c>
       <c r="M6" s="3" t="n">
-        <v>162.4</v>
+        <v>1.8</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>18.2</v>
@@ -978,10 +957,10 @@
         <v>86</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>481.1</v>
+        <v>47.1</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>21.8</v>
@@ -993,18 +972,20 @@
         <v>56.4</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="X6" s="8" t="n">
+      <c r="X6" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="Y6" s="3" t="n"/>
+      <c r="Y6" s="3" t="n">
+        <v>57.8</v>
+      </c>
       <c r="Z6" s="3" t="n">
         <v>14</v>
       </c>
@@ -1029,57 +1010,59 @@
         <v>17.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>24.1</v>
+        <v>14.1</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>8.6</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K7" s="8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>109.2</v>
+      <c r="K7" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54621561
+81
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P7" s="8" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="Q7" s="8" t="n">
+        <v>28341.2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>42.6</v>
+        <v>4.6</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="W7" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="W7" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1108,37 +1091,39 @@
       <c r="D8" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="8" t="n">
-        <v>17.8</v>
+      <c r="E8" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>20.9</v>
+        <v>23.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="I8" s="3" t="n"/>
+      <c r="I8" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="J8" s="3" t="n">
-        <v>19.2</v>
+        <v>1.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>18.6</v>
       </c>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N8" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>81.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>30.6</v>
@@ -1147,15 +1132,19 @@
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T8" s="3" t="n"/>
-      <c r="U8" s="3" t="n"/>
+        <v>1.7</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="V8" s="3" t="n">
-        <v>25.8</v>
+        <v>29.8</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>19.4</v>
+        <v>1.4</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>18.7</v>
@@ -1164,7 +1153,7 @@
         <v>56.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>1194.4</v>
+        <v>14.4</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1183,36 +1172,43 @@
       <c r="D9" s="10" t="n">
         <v>145.8</v>
       </c>
-      <c r="E9" s="11" t="n"/>
+      <c r="E9" s="10" t="n">
+        <v>88.7</v>
+      </c>
       <c r="F9" s="10" t="n">
-        <v>117.1</v>
+        <v>0.7</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>63.7</v>
+        <v>63</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>134.6</v>
+        <v>34.1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>256.4</v>
+        <v>56.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>1.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0.4</v>
+        <v>83.2</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1717
+20 4
+89 8 6
+</t>
+        </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>18.5</v>
+        <v>84.7</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
@@ -1221,31 +1217,31 @@
         <v>145.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>10.6</v>
+        <v>196.1</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>122.6</v>
+        <v>12.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>288.1</v>
+        <v>51</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>2938.1</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>73.5</v>
+        <v>13.4</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>970.1</v>
+        <v>914.4</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>95.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1.4</v>
+        <v>194.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1262,31 +1258,31 @@
       </c>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="10" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E10" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E10" s="10" t="n">
         <v>17.7</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>7.3</v>
+        <v>23.4</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>16.5</v>
+        <v>46.4</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>18.6</v>
+        <v>21.8</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>16.6</v>
@@ -1295,10 +1291,10 @@
         <v>18</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>84.7</v>
+        <v>820.1</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>29.2</v>
@@ -1307,28 +1303,28 @@
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>20.5</v>
+        <v>0.6</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>51</v>
+        <v>4.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>25.4</v>
+        <v>1.4</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>11.1</v>
+        <v>8.9</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>13.4</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1345,69 +1341,73 @@
       </c>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>16.8</v>
+        <v>6.4</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>4.6</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G11" s="3" t="n"/>
+        <v>23.1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>716.1</v>
+      </c>
       <c r="H11" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="I11" s="3" t="n"/>
+      <c r="I11" s="3" t="n">
+        <v>34.1</v>
+      </c>
       <c r="J11" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>18</v>
+        <v>86.09999999999999</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>890.1</v>
+        <v>89</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>44.1</v>
+        <v>0.4</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>6.8</v>
+        <v>48.4</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>900.6</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>18.4</v>
+        <v>700.6</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>48.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>47.5</v>
+        <v>5.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>20.2</v>
+        <v>1.1</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>600.1</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>13</v>
+        <v>1.3</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1430,39 +1430,39 @@
         <v>18</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>22.6</v>
+        <v>21.6</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>16.4</v>
+        <v>1.4</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>6.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
+        <v>21.8</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>49.9</v>
+        <v>14.6</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>17.4</v>
+        <v>1.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>89</v>
+        <v>23.5</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" s="8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q12" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1472,7 +1472,7 @@
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>57.1</v>
+        <v>58</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>16.2</v>
@@ -1481,13 +1481,13 @@
         <v>25.6</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>600.1</v>
+        <v>6</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>13</v>
@@ -1506,69 +1506,71 @@
         </is>
       </c>
       <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>17.2</v>
+      <c r="D13" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>1.4</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.4</v>
+        <v>1.4</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L13" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>19.8</v>
+      </c>
       <c r="M13" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>83.5</v>
+        <v>24.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>66</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>19.9</v>
+        <v>1.9</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>58</v>
+        <v>5.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>14.9</v>
+        <v>14</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>17.4</v>
+      <c r="W13" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>10.6</v>
@@ -1588,12 +1590,14 @@
       </c>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n">
-        <v>27.4</v>
+        <v>17.4</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F14" s="12" t="n"/>
+      <c r="F14" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="G14" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
@@ -1601,55 +1605,55 @@
         <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>19</v>
+        <v>10.9</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M14" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>74.5</v>
+        <v>213.4</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>26.8</v>
+        <v>46.2</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="S14" s="8" t="n">
-        <v>118.2</v>
+      <c r="S14" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>21.5</v>
+        <v>52.1</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>17</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>23.6</v>
+        <v>50.1</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X14" s="3" t="n">
-        <v>1.9</v>
+      <c r="X14" s="8" t="n">
+        <v>39.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>61.8</v>
+        <v>6</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1669,31 +1673,35 @@
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>17.8</v>
+        <v>18.8</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>11</v>
+        <v>23.6</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>10.2</v>
+        <v>1.6</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42292792
+64
+</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>64.59999999999999</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>18.6</v>
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>220.5</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>16.8</v>
@@ -1705,22 +1713,22 @@
         <v>84</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>13.4</v>
+        <v>72.2</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>21.2</v>
+      <c r="R15" s="8" t="n">
+        <v>12.6</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>22.1</v>
+        <v>111.9</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>25.4</v>
@@ -1732,10 +1740,10 @@
         <v>17.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>114.6</v>
+        <v>14.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1752,17 +1760,19 @@
       </c>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="10" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E16" s="11" t="n"/>
+        <v>38.8</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>19.2</v>
+      </c>
       <c r="F16" s="10" t="n">
-        <v>193.9</v>
+        <v>13.9</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>249.8</v>
+        <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>20.6</v>
@@ -1771,52 +1781,52 @@
         <v>50.6</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>220.3</v>
+        <v>18.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>84</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>72.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>138.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>102.1</v>
+        <v>132.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>28.8</v>
+        <v>988.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>211.9</v>
+        <v>53.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>814.4</v>
+        <v>813.4</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>122.8</v>
+        <v>12.8</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>933.5</v>
+        <v>93.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>55</v>
+        <v>202.5</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1835,26 +1845,30 @@
       <c r="D17" s="10" t="n">
         <v>27.8</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="10" t="n">
         <v>17.8</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>113.9</v>
+        <v>2.8</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>6.1</v>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+61
+</t>
+        </is>
       </c>
       <c r="J17" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>18.6</v>
@@ -1862,42 +1876,44 @@
       <c r="M17" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N17" s="3" t="n"/>
+      <c r="N17" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>84</v>
+        <v>284.6</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="R17" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="R17" s="8" t="n">
         <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>53.2</v>
+        <v>482.1</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>17.2</v>
+        <v>1.2</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>19.7</v>
+        <v>1.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1913,74 +1929,74 @@
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="9" t="n">
-        <v>30.55</v>
-      </c>
-      <c r="E18" s="9" t="n">
+      <c r="D18" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>13.6</v>
-      </c>
       <c r="H18" s="3" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>18.6</v>
+        <v>43.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.4</v>
+        <v>6</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.6</v>
+        <v>164.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>18.1</v>
+        <v>1</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>12.1</v>
+        <v>118.2</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>504.1</v>
+        <v>2.8</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>41.5</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>24.8</v>
+        <v>0.1</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>432.1</v>
+        <v>46.8</v>
       </c>
       <c r="U18" s="3" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="W18" s="8" t="n">
         <v>6.2</v>
       </c>
-      <c r="V18" s="3" t="n">
-        <v>864.1</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>20.2</v>
-      </c>
       <c r="X18" s="3" t="n">
-        <v>10.1</v>
+        <v>109.1</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>580.1</v>
+        <v>8</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>9.4</v>
+        <v>19.4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1996,72 +2012,72 @@
         </is>
       </c>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="8" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>17.8</v>
+      <c r="D19" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>17.6</v>
+        <v>13.1</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>0.4</v>
+        <v>13.5</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
+        <v>1.2</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="O19" s="3" t="n">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="R19" s="8" t="n">
-        <v>209.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>19.4</v>
+        <v>1.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>46.8</v>
+        <v>4.5</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>26.1</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2077,41 +2093,41 @@
         </is>
       </c>
       <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n">
-        <v>10.6</v>
+      <c r="D20" s="9" t="n">
+        <v>1.6</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>23.1</v>
+        <v>12.4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>11.9</v>
+        <v>8.6</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>71.90000000000001</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>12.6</v>
+        <v>1.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>18.1</v>
+        <v>1.4</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>881</v>
+        <v>80.8</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>2.8</v>
@@ -2123,28 +2139,28 @@
         <v>21.8</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>148.5</v>
+        <v>56</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>26.4</v>
+        <v>465.4</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>50.5</v>
+        <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>58.8</v>
+        <v>8</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2161,61 +2177,61 @@
       </c>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>417</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>26.5</v>
-      </c>
       <c r="R21" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>19.8</v>
+        <v>1.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v>15.9</v>
+        <v>68.3</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>74.40000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>18.6</v>
@@ -2224,7 +2240,7 @@
         <v>18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2250,67 +2266,67 @@
         <v>17.6</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>17</v>
+        <v>10.8</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>17.6</v>
+        <v>1.7</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>16.6</v>
+        <v>4.1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>18.8</v>
+        <v>72.40000000000001</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.2</v>
+        <v>23</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>19.8</v>
+        <v>18.2</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>188</v>
+        <v>2.8</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>2.6</v>
+        <v>7.3</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>19.8</v>
+        <v>12.5</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>68.3</v>
+        <v>267.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v>19.6</v>
+        <v>39</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>16.8</v>
+        <v>25.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>17.5</v>
+        <v>1.5</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>16</v>
+        <v>726.8</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>25.4</v>
+        <v>35.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2333,67 +2349,65 @@
         <v>99.40000000000001</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>110.8</v>
+        <v>117.6</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>568.2</v>
+        <v>56.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>84.8</v>
+        <v>34.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.2</v>
+        <v>32.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>52.9</v>
+        <v>5.9</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>93</v>
+        <v>1.6</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>285</v>
+        <v>185</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>18.8</v>
+        <v>357.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>126.8</v>
+        <v>0.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>7.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>740.8</v>
+        <v>740.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>103.9</v>
+        <v>113.4</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>111.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>96.7</v>
+        <v>68.3</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>975.1</v>
+        <v>175.1</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>95.59999999999999</v>
-      </c>
+        <v>1238.5</v>
+      </c>
+      <c r="W23" s="3" t="n"/>
       <c r="X23" s="3" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>30.5</v>
+        <v>3152.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>52.8</v>
+        <v>62.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2410,73 +2424,73 @@
       </c>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="10" t="n">
-        <v>29.1</v>
+        <v>2.1</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>17.9</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>17.6</v>
+        <v>28.5</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.9</v>
+        <v>11.7</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>52.9</v>
+        <v>6.6</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>6.8</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>28.1</v>
+        <v>0.8</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>20.7</v>
+        <v>0.3</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>53.5</v>
+        <v>3.5</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>24.7</v>
+        <v>4.7</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>19.1</v>
+        <v>3.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.9</v>
+        <v>0.8</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>12.8</v>
+        <v>121.6</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2492,21 +2506,23 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>45.6</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>18.8</v>
+      <c r="F25" s="9" t="n">
+        <v>4.8</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>26.1</v>
+        <v>16.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.2</v>
@@ -2515,46 +2531,46 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>16.2</v>
+        <v>47.1</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>18.4</v>
+        <v>16.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>83.5</v>
+        <v>356.4</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>34.1</v>
+        <v>54.1</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>19.4</v>
+        <v>0.8</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>605.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>0.2</v>
+        <v>138.1</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>13.9</v>
+        <v>438.1</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>88.8</v>
+        <v>8.9</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>2.8</v>
@@ -2573,44 +2589,44 @@
         </is>
       </c>
       <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n">
-        <v>28.8</v>
+      <c r="D26" s="9" t="n">
+        <v>68.8</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F26" s="9" t="n">
-        <v>48.4</v>
+      <c r="F26" s="8" t="n">
+        <v>30.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16</v>
+        <v>11.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>304.1</v>
+        <v>0.1</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>16.8</v>
+      <c r="M26" s="8" t="n">
+        <v>68.09999999999999</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>16.1</v>
+        <v>18.9</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
@@ -2619,7 +2635,7 @@
         <v>21.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>8</v>
+        <v>20.7</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>52.2</v>
@@ -2627,20 +2643,20 @@
       <c r="U26" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V26" s="3" t="n">
-        <v>24.4</v>
+      <c r="V26" s="8" t="n">
+        <v>4494.4</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>19.6</v>
+        <v>18.6</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>28.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>12.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2656,43 +2672,47 @@
         </is>
       </c>
       <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>21.4</v>
-      </c>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G27" s="8" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>465.4</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>194.6</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>27.4</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>20.8</v>
@@ -2703,7 +2723,7 @@
       <c r="T27" s="3" t="n">
         <v>56.7</v>
       </c>
-      <c r="U27" s="3" t="n">
+      <c r="U27" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="V27" s="3" t="n">
@@ -2713,7 +2733,7 @@
         <v>19.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>20.1</v>
+        <v>22.1</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>64</v>
@@ -2736,71 +2756,73 @@
       </c>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>22.8</v>
+        <v>14.4</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>16</v>
+      <c r="H28" s="8" t="n">
+        <v>60.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>24</v>
+        <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="8" t="n">
+      <c r="L28" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M28" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="O28" s="3" t="n"/>
+      <c r="M28" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="P28" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>27.4</v>
+        <v>22.4</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>20.7</v>
+        <v>0.7</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v>95.59999999999999</v>
+        <v>56.1</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>59</v>
+        <v>52.5</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2819,11 +2841,11 @@
       <c r="D29" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="E29" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>22.9</v>
+      <c r="E29" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>9.4</v>
@@ -2832,22 +2854,22 @@
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.4</v>
+        <v>424.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>19.9</v>
+        <v>12.1</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>89</v>
@@ -2865,22 +2887,22 @@
         <v>19.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>29.2</v>
+        <v>5.5</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="V29" s="8" t="n">
-        <v>229.6</v>
+      <c r="V29" s="3" t="n">
+        <v>43.6</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>19.6</v>
+        <v>12.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>66.2</v>
+        <v>6.2</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>9.800000000000001</v>
@@ -2900,71 +2922,73 @@
       </c>
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="10" t="n">
-        <v>133.4</v>
+        <v>1353.2</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>85.8</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>22.1</v>
+        <v>2.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>47.4</v>
+        <v>31.6</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>33</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>9.1</v>
+        <v>41.7</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>2.8</v>
+        <v>89</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>115.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>139</v>
+        <v>139.1</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>102.4</v>
+        <v>19.6</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>298</v>
+        <v>5.5</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="V30" s="3" t="n"/>
+        <v>28.1</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>118.2</v>
+      </c>
       <c r="W30" s="3" t="n">
-        <v>95</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>5.6</v>
+        <v>34.6</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>45.1</v>
+        <v>4981.1</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2981,71 +3005,71 @@
       </c>
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="10" t="n">
-        <v>26.6</v>
+        <v>2.6</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>17.2</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>9.6</v>
+        <v>1.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H31" s="8" t="n">
-        <v>10.6</v>
+      <c r="H31" s="3" t="n">
+        <v>876.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="n">
+        <v>7.1</v>
+      </c>
       <c r="L31" s="3" t="n">
-        <v>944.1</v>
+        <v>94</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="O31" s="3" t="n"/>
       <c r="P31" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>26.4</v>
+        <v>6.4</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>20.4</v>
+        <v>2.4</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>20.4</v>
+        <v>2.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>59.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.4</v>
+        <v>14.2</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>23.6</v>
+        <v>43.6</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>19.8</v>
+        <v>8.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>67.2</v>
+        <v>0.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3061,10 +3085,10 @@
         </is>
       </c>
       <c r="C32" s="3" t="n"/>
-      <c r="D32" s="13" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E32" s="13" t="n">
+      <c r="D32" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="F32" s="3" t="n">
@@ -3074,49 +3098,49 @@
         <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>26.7</v>
+        <v>1.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>482.4</v>
+        <v>1.8</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>18.4</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>92.40000000000001</v>
+        <v>28.5</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>19.8</v>
+        <v>1.2</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>56.8</v>
+        <v>6.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>18.8</v>
@@ -3125,7 +3149,7 @@
         <v>19.5</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>71</v>
+        <v>21.8</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>8</v>
@@ -3144,29 +3168,29 @@
         </is>
       </c>
       <c r="C33" s="3" t="n"/>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="E33" s="13" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>21.9</v>
+      <c r="E33" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>1.9</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>15.2</v>
+        <v>1.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.4</v>
@@ -3175,41 +3199,43 @@
         <v>565.1</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>11.8</v>
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>84</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q33" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q33" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="V33" s="3" t="n"/>
+      <c r="V33" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="W33" s="3" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>75</v>
+        <v>16.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3225,56 +3251,56 @@
         </is>
       </c>
       <c r="C34" s="3" t="n"/>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>21.9</v>
+        <v>23.1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>57.2</v>
+        <v>57.6</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>15.3</v>
@@ -3283,16 +3309,16 @@
         <v>24.6</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>20</v>
+        <v>18.6</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>10.2</v>
+        <v>16.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3308,72 +3334,74 @@
         </is>
       </c>
       <c r="C35" s="3" t="n"/>
-      <c r="D35" s="13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E35" s="13" t="n">
+      <c r="D35" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>23.1</v>
+        <v>14.1</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="H35" s="8" t="n">
-        <v>17</v>
+      <c r="H35" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="L35" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="N35" s="3" t="n"/>
+      <c r="N35" s="3" t="n">
+        <v>18.3</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>900.6</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>24.2</v>
+        <v>4.2</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>20.4</v>
+        <v>6.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>20.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>86.5</v>
+        <v>6</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>3.2</v>
+        <v>32.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3389,61 +3417,63 @@
         </is>
       </c>
       <c r="C36" s="3" t="n"/>
-      <c r="D36" s="13" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E36" s="13" t="n">
+      <c r="D36" s="9" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>20.9</v>
+      <c r="F36" s="9" t="n">
+        <v>2.6</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>10.8</v>
+        <v>11.8</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N36" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="N36" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>87</v>
+        <v>83.5</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>12.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>21.8</v>
+        <v>61.8</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>22.1</v>
+        <v>2.1</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>56.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="V36" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>20.4</v>
+      </c>
       <c r="W36" s="3" t="n">
         <v>18.8</v>
       </c>
@@ -3451,10 +3481,10 @@
         <v>20.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>4.2</v>
+        <v>35.2</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3471,25 +3501,25 @@
       </c>
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="10" t="n">
-        <v>112.8</v>
-      </c>
-      <c r="E37" s="13" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="E37" s="10" t="n">
         <v>88.2</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>23.2</v>
+        <v>2.6</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>45.6</v>
+        <v>456.1</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>5.9</v>
+        <v>20.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>31.2</v>
+        <v>3.1</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>18.6</v>
@@ -3498,41 +3528,43 @@
         <v>18.6</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>846.1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>595.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1139.5</v>
+        <v>87</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>131.8</v>
+        <v>134.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>102.2</v>
+        <v>1922.8</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="T37" s="3" t="n"/>
+        <v>7.7</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>56.4</v>
+      </c>
       <c r="U37" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>709.6</v>
+        <v>713.6</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>101.6</v>
+        <v>18.8</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>386.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>7.9</v>
+        <v>86.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3551,71 +3583,83 @@
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="13" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E38" s="13" t="n">
-        <v>17.6</v>
+      <c r="D38" s="10" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>1.6</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G38" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G38" s="8" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>895</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>20.9</v>
+      <c r="H38" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+9
+</t>
+        </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.7</v>
+        <v>27.3</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>16.5</v>
+        <v>1.5</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>737.8</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q38" s="3" t="n">
-        <v>26.8</v>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+248
+</t>
+        </is>
       </c>
       <c r="R38" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>28.3</v>
+        <v>0.6</v>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+203
+</t>
+        </is>
       </c>
       <c r="T38" s="3" t="n">
-        <v>5.7</v>
+        <v>57.8</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>14.9</v>
+        <v>4.7</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>11.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>20.3</v>
+        <v>2.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7.9</v>
+        <v>0.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.2</v>
@@ -3637,17 +3681,17 @@
       <c r="D39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="E39" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F39" s="8" t="n">
-        <v>22.6</v>
+      <c r="F39" s="9" t="n">
+        <v>42.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>4.2</v>
@@ -3656,52 +3700,52 @@
         <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>9.6</v>
+        <v>27.3</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="M39" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R39" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>2208.4</v>
-      </c>
       <c r="S39" s="3" t="n">
-        <v>19.8</v>
+        <v>13.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>114.9</v>
+        <v>1.9</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="V39" s="8" t="n">
-        <v>39.4</v>
+        <v>35.4</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>28.5</v>
+        <v>19.6</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>181.1</v>
+        <v>64.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3723,68 +3767,68 @@
       <c r="E40" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>71.8</v>
+      <c r="F40" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>16.8</v>
+        <v>1.8</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5.4</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>194.1</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N40" s="8" t="n">
+        <v>194.5</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N40" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="P40" s="8" t="n">
-        <v>126.2</v>
+        <v>84</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>20</v>
+        <v>6.6</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>61.6</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>56.8</v>
+        <v>5.8</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>28.8</v>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v>35.4</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>20.1</v>
+        <v>11.6</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>81.5</v>
+        <v>14.4</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3800,70 +3844,72 @@
         </is>
       </c>
       <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E41" s="8" t="n">
+      <c r="D41" s="9" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E41" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F41" s="12" t="n"/>
+      <c r="F41" s="3" t="n">
+        <v>21.3</v>
+      </c>
       <c r="G41" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>59.5</v>
+        <v>1.8</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>17.2</v>
+      <c r="M41" s="8" t="n">
+        <v>72.09999999999999</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>15.9</v>
+        <v>18.7</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>81</v>
+        <v>840.1</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>22.6</v>
+        <v>0.3</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>17.6</v>
+        <v>12.6</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.9</v>
+        <v>57.8</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>19.6</v>
+        <v>14.4</v>
       </c>
       <c r="V41" s="3" t="n"/>
       <c r="W41" s="3" t="n">
-        <v>16.8</v>
+        <v>18.6</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>19.6</v>
+        <v>76.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.5</v>
+        <v>81.5</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>14.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3879,47 +3925,47 @@
         </is>
       </c>
       <c r="C42" s="3" t="n"/>
-      <c r="D42" s="8" t="n">
+      <c r="D42" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>22.9</v>
+        <v>18.1</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>70.8</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>14</v>
+        <v>1.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>16.4</v>
+        <v>23.5</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>13</v>
+        <v>24.2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>28.6</v>
+        <v>0.3</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>21</v>
@@ -3928,22 +3974,26 @@
         <v>20.4</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U42" s="8" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="V42" s="3" t="n"/>
+      <c r="V42" s="3" t="n">
+        <v>6.9</v>
+      </c>
       <c r="W42" s="3" t="n">
-        <v>20</v>
+        <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>19.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3962,69 +4012,71 @@
         <v>30.4</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G43" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G43" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J43" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J43" s="3" t="n">
         <v>15</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>16.4</v>
+        <v>12.4</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>13.9</v>
+        <v>1.9</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>85</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>4.9</v>
+        <v>28.6</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>0.6</v>
+        <v>30.6</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>20.6</v>
+        <v>21.8</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>18.9</v>
+        <v>2.9</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>142.6</v>
+        <v>42.6</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>26.4</v>
+        <v>6.9</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X43" s="8" t="n">
-        <v>427</v>
+      <c r="X43" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4039,63 +4091,69 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="G44" s="3" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="H44" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>7.6</v>
+      <c r="I44" s="8" t="n">
+        <v>125.6</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.3</v>
+        <v>1.3</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>18.8</v>
+        <v>11.8</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="P44" s="8" t="n">
-        <v>65</v>
+        <v>80</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>765</v>
-      </c>
-      <c r="R44" s="8" t="n">
-        <v>21.8</v>
+        <v>766.1</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>157.1</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>20.9</v>
+        <v>62.6</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="V44" s="8" t="n">
-        <v>14.8</v>
+      <c r="V44" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X44" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y44" s="3" t="n">
         <v>14.8</v>
       </c>
@@ -4115,74 +4173,76 @@
       </c>
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="10" t="n">
-        <v>24.8</v>
+        <v>28.6</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>17.1</v>
+        <v>1.1</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>92.2</v>
+        <v>32.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>33.5</v>
+        <v>3.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.9</v>
+        <v>61.3</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>499.6</v>
+        <v>139.6</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>998.4</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>52.6</v>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+41 1
+</t>
+        </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>165</v>
+        <v>21.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>765</v>
+        <v>27.5</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>111.1</v>
+        <v>26.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>16.2</v>
+        <v>1.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>107.1</v>
+        <v>317.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>143.9</v>
+        <v>23.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>114.8</v>
+        <v>1.1</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>19.1</v>
+        <v>4</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>65.5</v>
+        <v>0.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>10.4</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4198,16 +4258,20 @@
       </c>
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="10" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>17.1</v>
+        <v>2.9</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+6
+</t>
+        </is>
       </c>
       <c r="F46" s="10" t="n">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4218,51 +4282,62 @@
       <c r="J46" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="n">
+        <v>9.4</v>
+      </c>
       <c r="L46" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>7.8</v>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+41 1
+</t>
+        </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>21.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>28.6</v>
+        <v>0.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>20.1</v>
+        <v>157.1</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>15.8</v>
+        <v>1.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>917.9</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V46" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2919292795
+24
+12
+</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>19.1</v>
+        <v>1.9</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>65.5</v>
+        <v>0.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>10.4</v>
+        <v>0.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -47,20 +47,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -771,37 +771,61 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="n">
+        <v>5.4</v>
+      </c>
       <c r="D4" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+        <v>27.8</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="G4" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+      <c r="H4" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="M4" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="O4" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="P4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="n">
+        <v>513.9</v>
+      </c>
       <c r="Q4" s="3" t="n">
-        <v>27.8</v>
+        <v>21.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" s="3" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
@@ -821,32 +845,56 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="G5" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="K5" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>83</v>
+      </c>
       <c r="P5" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q5" s="3" t="inlineStr"/>
+        <v>12.7</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>28.4</v>
+      </c>
       <c r="R5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="T5" s="3" t="n">
-        <v>54.8</v>
+        <v>56.8</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>16.8</v>
@@ -854,7 +902,7 @@
       <c r="V5" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -880,44 +928,62 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr"/>
+      <c r="D6" s="9" t="n">
+        <v>0.8</v>
+      </c>
       <c r="E6" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="8" t="n">
+      <c r="F6" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>7.4</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>28.6</v>
+      </c>
       <c r="R6" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S6" s="3" t="inlineStr"/>
+        <v>21.8</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="T6" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U6" s="8" t="n">
+        <v>656.4</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>20</v>
@@ -945,50 +1011,72 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="9" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H7" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="L7" s="8" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>484.1</v>
+      </c>
       <c r="N7" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O7" s="3" t="inlineStr"/>
+        <v>19.2</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>89</v>
+      </c>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>18.5</v>
+      </c>
       <c r="T7" s="3" t="n">
-        <v>146.4</v>
+        <v>142.6</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="W7" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>27.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1005,47 +1093,61 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="8" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>13.8</v>
+      </c>
       <c r="H8" s="8" t="n">
-        <v>95.40000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
+        <v>15.1</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>81</v>
+      </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="R8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="n">
+        <v>21.2</v>
+      </c>
       <c r="S8" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>24.2</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>25.8</v>
+      </c>
       <c r="W8" s="3" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>19.3</v>
+        <v>18.7</v>
       </c>
       <c r="Y8" s="3" t="inlineStr"/>
       <c r="Z8" s="3" t="n">
@@ -1065,68 +1167,74 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="11" t="n">
-        <v>145.8</v>
-      </c>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr"/>
+      <c r="D9" s="10" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>115.2</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>27.1</v>
+        <v>57.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>824.4</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>565.4</v>
+        <v>26.6</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>34.1</v>
+        <v>91.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
+        <v>82.2</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>89.8</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>122.9</v>
+        <v>42.3</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1943.8</v>
+        <v>142.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1096</v>
+        <v>106</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>19.7</v>
+        <v>100.8</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>201.1</v>
+        <v>2099.1</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>24.2</v>
+        <v>992.6</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>12.2</v>
+        <v>12.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>911.4</v>
+        <v>11.4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>18.7</v>
+        <v>19.1</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0.4</v>
+        <v>229.9</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>14.4</v>
+        <v>615</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1142,70 +1250,74 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="11" t="n">
-        <v>145.8</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>27.1</v>
+      <c r="D10" s="10" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>824.4</v>
+        <v>16.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>34.1</v>
+        <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>565.4</v>
+        <v>11.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>18.6</v>
+        <v>0.5</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>34.1</v>
+        <v>18</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+        <v>16.6</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>122.9</v>
+        <v>84.7</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q10" s="8" t="n">
-        <v>943.8</v>
-      </c>
-      <c r="R10" s="8" t="n">
-        <v>96</v>
-      </c>
-      <c r="S10" s="8" t="n">
-        <v>102.6</v>
+        <v>7.2</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>20.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>163.1</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>29461</v>
+        <v>51</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>12.2</v>
+        <v>25.4</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>911.4</v>
-      </c>
-      <c r="X10" s="3" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="Y10" s="3" t="n">
-        <v>0.4</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>165</v>
+        <v>13.9</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1221,57 +1333,63 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="10" t="inlineStr"/>
+      <c r="D11" s="12" t="n">
+        <v>28.4</v>
+      </c>
       <c r="E11" s="3" t="n">
-        <v>17.7</v>
+        <v>16.8</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
+        <v>22.6</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H11" s="3" t="n">
-        <v>16.8</v>
+        <v>13.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>16.9</v>
+        <v>5.4</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O11" s="3" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
+        <v>890.9</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q11" s="8" t="n">
-        <v>29.2</v>
+        <v>18.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="3" t="n">
-        <v>19.9</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="W11" s="3" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1285,65 +1403,75 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="10" t="inlineStr"/>
+      <c r="C12" s="3" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>28.2</v>
+      </c>
       <c r="E12" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J12" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>182</v>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="P12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="Q12" s="3" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="S12" s="8" t="n">
-        <v>18.4</v>
+        <v>21.6</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>2941.2</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>19.1</v>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>97.09999999999999</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>28.9</v>
+        <v>60</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>13.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1358,59 +1486,77 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="10" t="inlineStr"/>
-      <c r="E13" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="8" t="n">
-        <v>11.6</v>
+      <c r="C13" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>41.2</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J13" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>182</v>
+        <v>9.6</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
+        <v>283.5</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>41.4</v>
+      </c>
       <c r="Q13" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="R13" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>18.4</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>2941.2</v>
-      </c>
-      <c r="U13" s="3" t="inlineStr"/>
+        <v>51.1</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="V13" s="8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W13" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W13" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="X13" s="3" t="inlineStr"/>
-      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>60</v>
+      </c>
       <c r="Z13" s="3" t="n">
-        <v>13.8</v>
+        <v>1.3</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1426,58 +1572,74 @@
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="D14" s="12" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="H14" s="3" t="n">
-        <v>16.4</v>
+        <v>27.8</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>191.6</v>
+        <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="n">
-        <v>19.2</v>
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>87.8</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="8" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>24.9</v>
+        <v>74.5</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>51.1</v>
+        <v>58</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>14</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="W14" s="3" t="inlineStr"/>
+        <v>22.6</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>3.4</v>
+      </c>
       <c r="X14" s="3" t="n">
-        <v>19.1</v>
+        <v>16.8</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>13.8</v>
+        <v>10.6</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1493,52 +1655,72 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
+      <c r="D15" s="12" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>17.8</v>
+      </c>
       <c r="F15" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="I15" s="3" t="n">
-        <v>16</v>
+        <v>6.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
+        <v>10.2</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="N15" s="3" t="n">
-        <v>16.9</v>
+        <v>18.1</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>28.8</v>
+      </c>
       <c r="R15" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="S15" s="3" t="inlineStr"/>
+        <v>21.2</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>20.7</v>
+      </c>
       <c r="T15" s="3" t="n">
-        <v>58</v>
+        <v>52.1</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr"/>
+        <v>25.4</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>19.3</v>
+      </c>
       <c r="Y15" s="3" t="n">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>10.6</v>
+        <v>114.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1554,46 +1736,74 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="11" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="E16" s="12" t="inlineStr"/>
-      <c r="F16" s="12" t="inlineStr"/>
+      <c r="D16" s="10" t="n">
+        <v>1198.8</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>1113.9</v>
+      </c>
       <c r="G16" s="3" t="n">
-        <v>1191</v>
+        <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>117.6</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>900.6</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>980.8</v>
+      </c>
       <c r="M16" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>2281.2</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>104.1</v>
+      </c>
       <c r="S16" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>86.2</v>
+      </c>
       <c r="V16" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="W16" s="3" t="inlineStr"/>
+        <v>152.8</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>94.5</v>
+      </c>
       <c r="X16" s="3" t="n">
-        <v>187.8</v>
+        <v>92.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>25</v>
+        <v>304.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>114.6</v>
+        <v>14.1</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1608,69 +1818,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="8" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>134.4</v>
+      <c r="C17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>22.8</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>49.8</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>10.6</v>
+        <v>16.8</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>6.1</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>10.1</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="M17" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O17" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>128.2</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>98.8</v>
+        <v>13.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>266.2</v>
-      </c>
-      <c r="U17" s="3" t="inlineStr"/>
-      <c r="V17" s="8" t="n">
-        <v>22.8</v>
+        <v>52.2</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>148.1</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>99.3</v>
+        <v>12</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>302</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>61</v>
+        <v>12.2</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1685,54 +1901,74 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="n">
-        <v>27.8</v>
+      <c r="C18" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>80.40000000000001</v>
       </c>
       <c r="E18" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="N18" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr"/>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>14.6</v>
+      </c>
       <c r="Q18" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr"/>
-      <c r="U18" s="3" t="inlineStr"/>
+        <v>20.4</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>22.2</v>
+      </c>
       <c r="V18" s="3" t="n">
-        <v>24.6</v>
+        <v>26.4</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="n">
-        <v>160.4</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>12.2</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1748,47 +1984,71 @@
       </c>
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="n">
-        <v>12.5</v>
+        <v>29.6</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="K19" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="T19" s="3" t="n">
         <v>46.8</v>
       </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="n">
-        <v>2948.1</v>
-      </c>
-      <c r="U19" s="3" t="inlineStr"/>
-      <c r="V19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>26.1</v>
+      </c>
       <c r="W19" s="3" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y19" s="3" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>34</v>
+      </c>
       <c r="Z19" s="3" t="n">
-        <v>1149.5</v>
+        <v>19.9</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -1804,40 +2064,72 @@
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>24.4</v>
+      </c>
       <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
+      <c r="H20" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>7.9</v>
+      </c>
       <c r="J20" s="3" t="n">
-        <v>17.8</v>
+        <v>12.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>20.9</v>
+      </c>
       <c r="T20" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="U20" s="3" t="inlineStr"/>
-      <c r="V20" s="3" t="inlineStr"/>
-      <c r="W20" s="3" t="inlineStr"/>
+        <v>48.8</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>20.2</v>
+      </c>
       <c r="X20" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Y20" s="3" t="n">
+        <v>58</v>
+      </c>
       <c r="Z20" s="3" t="n">
-        <v>16</v>
+        <v>14.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -1853,38 +2145,72 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="8" t="n">
+      <c r="D21" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z21" s="3" t="n">
         <v>12.6</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="n">
-        <v>288</v>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>948.5</v>
-      </c>
-      <c r="U21" s="3" t="inlineStr"/>
-      <c r="V21" s="3" t="inlineStr"/>
-      <c r="W21" s="3" t="inlineStr"/>
-      <c r="X21" s="3" t="inlineStr"/>
-      <c r="Y21" s="3" t="inlineStr"/>
-      <c r="Z21" s="3" t="n">
-        <v>114.9</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -1900,42 +2226,72 @@
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="J22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
+        <v>7.4</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="T22" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="U22" s="3" t="inlineStr"/>
+        <v>68.3</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="V22" s="3" t="n">
-        <v>24.4</v>
+        <v>19.6</v>
       </c>
       <c r="W22" s="8" t="n">
-        <v>18.6</v>
+        <v>16.8</v>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
       <c r="Y22" s="3" t="n">
-        <v>39</v>
+        <v>16.8</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>12.6</v>
+        <v>5.7</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -1950,51 +2306,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="12" t="inlineStr"/>
-      <c r="E23" s="12" t="inlineStr"/>
-      <c r="F23" s="12" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>195.6</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>11.1</v>
+      </c>
       <c r="G23" s="3" t="n">
-        <v>10.8</v>
+        <v>26.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
+        <v>84.8</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>92.09999999999999</v>
+      </c>
       <c r="J23" s="3" t="n">
-        <v>1.4</v>
+        <v>52.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
+        <v>926.8</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>140.4</v>
+      </c>
       <c r="R23" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="S23" s="3" t="inlineStr"/>
+        <v>103.4</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>1180.4</v>
+      </c>
       <c r="T23" s="3" t="n">
-        <v>168.3</v>
-      </c>
-      <c r="U23" s="3" t="inlineStr"/>
+        <v>267.9</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>91.90000000000001</v>
+      </c>
       <c r="V23" s="3" t="n">
-        <v>19.6</v>
+        <v>123.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>116.8</v>
-      </c>
-      <c r="X23" s="3" t="inlineStr"/>
+        <v>20.6</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>41.8</v>
+      </c>
       <c r="Y23" s="3" t="n">
-        <v>16</v>
+        <v>2216.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>5.4</v>
+        <v>24.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2009,71 +2391,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="8" t="n">
-        <v>945.6</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>26.6</v>
+      <c r="C24" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>31.1</v>
+        <v>6.6</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>20.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr"/>
-      <c r="O24" s="3" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>85.40000000000001</v>
+      </c>
       <c r="P24" s="3" t="n">
-        <v>156.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="R24" s="8" t="n">
-        <v>103.4</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>80.40000000000001</v>
+        <v>28.1</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>1267.8</v>
+        <v>53.5</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="W24" s="8" t="n">
-        <v>20.6</v>
+        <v>18.5</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>94.8</v>
+        <v>18.9</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>302</v>
+        <v>61</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>52.8</v>
+        <v>12.6</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2088,58 +2474,70 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="n">
+        <v>81.5</v>
+      </c>
       <c r="D25" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H25" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>6.6</v>
+        <v>19.6</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>20.8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
+        <v>3.2</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="L25" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>82.90000000000001</v>
+      </c>
       <c r="P25" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>28.1</v>
+        <v>3.4</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>221.8</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>20.7</v>
+        <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T25" s="3" t="inlineStr"/>
-      <c r="U25" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V25" s="3" t="inlineStr"/>
-      <c r="W25" s="3" t="n">
-        <v>19.1</v>
+        <v>20.9</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>86.40000000000001</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
       <c r="Y25" s="3" t="inlineStr"/>
-      <c r="Z25" s="3" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2153,46 +2551,78 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>10.2</v>
+      </c>
       <c r="H26" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
+        <v>16.1</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J26" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr"/>
+        <v>82.40000000000001</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="M26" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
-      <c r="O26" s="3" t="inlineStr"/>
-      <c r="P26" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="Q26" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R26" s="3" t="inlineStr"/>
+        <v>28.8</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>21.2</v>
+      </c>
       <c r="S26" s="3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>13.8</v>
+        <v>12.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="V26" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>29.4</v>
+      </c>
       <c r="W26" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X26" s="3" t="inlineStr"/>
-      <c r="Y26" s="3" t="inlineStr"/>
-      <c r="Z26" s="3" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>112.8</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2206,46 +2636,70 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="G27" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+        <v>10.2</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="I27" s="3" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M27" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="R27" s="3" t="inlineStr"/>
+      <c r="N27" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="n">
+        <v>20.8</v>
+      </c>
       <c r="S27" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>12.2</v>
+        <v>56.9</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V27" s="3" t="inlineStr"/>
-      <c r="W27" s="3" t="inlineStr"/>
-      <c r="X27" s="3" t="inlineStr"/>
+        <v>12.8</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="Y27" s="3" t="inlineStr"/>
       <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2262,37 +2716,67 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F28" s="11" t="inlineStr"/>
       <c r="G28" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr"/>
+        <v>9.4</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="I28" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr"/>
-      <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr"/>
-      <c r="O28" s="3" t="inlineStr"/>
-      <c r="P28" s="3" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>5294</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>9.4</v>
+      </c>
       <c r="Q28" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R28" s="3" t="inlineStr"/>
-      <c r="S28" s="3" t="inlineStr"/>
-      <c r="T28" s="3" t="inlineStr"/>
+        <v>21.4</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>56.7</v>
+      </c>
       <c r="U28" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V28" s="3" t="inlineStr"/>
-      <c r="W28" s="3" t="inlineStr"/>
-      <c r="X28" s="3" t="inlineStr"/>
+        <v>15.8</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y28" s="3" t="inlineStr"/>
       <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2309,37 +2793,75 @@
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="8" t="n">
-        <v>16.6</v>
+      <c r="D29" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="O29" s="3" t="inlineStr"/>
-      <c r="P29" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q29" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr"/>
-      <c r="T29" s="3" t="inlineStr"/>
+        <v>25.6</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>659.5</v>
+      </c>
       <c r="U29" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X29" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="V29" s="3" t="inlineStr"/>
-      <c r="W29" s="3" t="inlineStr"/>
-      <c r="X29" s="3" t="inlineStr"/>
-      <c r="Y29" s="3" t="inlineStr"/>
-      <c r="Z29" s="3" t="inlineStr"/>
+      <c r="Y29" s="3" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2354,52 +2876,74 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="12" t="inlineStr"/>
-      <c r="E30" s="12" t="inlineStr"/>
-      <c r="F30" s="12" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="3" t="inlineStr"/>
+      <c r="D30" s="10" t="n">
+        <v>1952.4</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>1816.8</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>131</v>
+      </c>
       <c r="I30" s="3" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr"/>
+        <v>2016.1</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>2681.4</v>
+      </c>
       <c r="K30" s="3" t="n">
-        <v>0</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>18.6</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>17.4</v>
+        <v>836.5</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P30" s="3" t="inlineStr"/>
+        <v>420</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="Q30" s="3" t="n">
-        <v>125.6</v>
+        <v>132</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>19.8</v>
+        <v>1082</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="T30" s="3" t="inlineStr"/>
+        <v>102.2</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>298.9</v>
+      </c>
       <c r="U30" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="V30" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>1818.2</v>
+      </c>
       <c r="W30" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X30" s="3" t="inlineStr"/>
-      <c r="Y30" s="3" t="inlineStr"/>
+        <v>985.6</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>316.2</v>
+      </c>
       <c r="Z30" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>49.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2414,59 +2958,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="8" t="n">
-        <v>309.8</v>
-      </c>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="8" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>810</v>
+      <c r="C31" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>26.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>6.6</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="8" t="n">
+        <v>318.3</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="inlineStr"/>
-      <c r="P31" s="8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" s="3" t="inlineStr"/>
-      <c r="T31" s="3" t="inlineStr"/>
+        <v>16.7</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>59.8</v>
+      </c>
       <c r="U31" s="3" t="n">
-        <v>30.4</v>
+        <v>19.2</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>1.5</v>
+        <v>23.6</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="X31" s="3" t="inlineStr"/>
-      <c r="Y31" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>69.2</v>
+      </c>
       <c r="Z31" s="3" t="n">
-        <v>249.8</v>
+        <v>10</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2481,54 +3041,76 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>5.6</v>
+      </c>
       <c r="H32" s="3" t="n">
-        <v>26.8</v>
+        <v>15.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>94</v>
+        <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="W32" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M32" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
-      <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="3" t="inlineStr"/>
-      <c r="S32" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="T32" s="3" t="inlineStr"/>
-      <c r="U32" s="8" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="W32" s="3" t="inlineStr"/>
-      <c r="X32" s="3" t="inlineStr"/>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="X32" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -2542,62 +3124,74 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>23.1</v>
+      </c>
       <c r="G33" s="3" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18.2</v>
+        <v>17.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>16.9</v>
+        <v>2</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>18.4</v>
+        <v>17.4</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N33" s="3" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16.7</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>86.8</v>
+        <v>84</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>2.7</v>
+        <v>28.6</v>
       </c>
       <c r="R33" s="8" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>12.8</v>
+        <v>19.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56.8</v>
+        <v>56</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X33" s="3" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -2614,39 +3208,69 @@
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>17.4</v>
+        <v>18.4</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N34" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O34" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R34" s="3" t="inlineStr"/>
-      <c r="S34" s="3" t="inlineStr"/>
-      <c r="T34" s="3" t="inlineStr"/>
-      <c r="U34" s="3" t="inlineStr"/>
-      <c r="V34" s="3" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R34" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>284.6</v>
+      </c>
       <c r="W34" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X34" s="3" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="Y34" s="3" t="inlineStr"/>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -2662,41 +3286,71 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>17.8</v>
+      </c>
       <c r="F35" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr"/>
+        <v>21.8</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>5.2</v>
+      </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="8" t="n">
-        <v>17.2</v>
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N35" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="P35" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="S35" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="O35" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr"/>
-      <c r="T35" s="3" t="inlineStr"/>
-      <c r="U35" s="3" t="inlineStr"/>
-      <c r="V35" s="3" t="inlineStr"/>
-      <c r="W35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="W35" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="X35" s="3" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Y35" s="3" t="inlineStr"/>
       <c r="Z35" s="3" t="inlineStr"/>
@@ -2713,35 +3367,75 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="P36" s="3" t="inlineStr"/>
-      <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr"/>
-      <c r="T36" s="3" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>26.4</v>
+      </c>
       <c r="U36" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="V36" s="3" t="inlineStr"/>
-      <c r="W36" s="3" t="inlineStr"/>
+        <v>460.8</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="X36" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="Y36" s="3" t="inlineStr"/>
+        <v>20.8</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>86.5</v>
+      </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -2757,41 +3451,75 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="12" t="inlineStr"/>
-      <c r="E37" s="12" t="inlineStr"/>
-      <c r="F37" s="12" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
+      <c r="D37" s="10" t="n">
+        <v>1120.8</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>111</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>808</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>21816.4</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>219.8</v>
+      </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>118.2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>90.5</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>1082.2</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="3" t="inlineStr"/>
-      <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr"/>
+        <v>4920.8</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>1102.2</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>101.9</v>
+      </c>
       <c r="T37" s="3" t="n">
-        <v>26.4</v>
+        <v>288.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V37" s="3" t="inlineStr"/>
-      <c r="W37" s="3" t="inlineStr"/>
+        <v>14.1</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>19.4</v>
+      </c>
       <c r="X37" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Y37" s="3" t="inlineStr"/>
-      <c r="Z37" s="3" t="inlineStr"/>
+        <v>10.1</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>231.2</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2806,59 +3534,73 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="8" t="n">
-        <v>130.8</v>
-      </c>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="8" t="n">
-        <v>48.6</v>
+      <c r="D38" s="10" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>41.5</v>
+        <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="K38" s="8" t="n">
-        <v>15.4</v>
+        <v>6.9</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>95.09999999999999</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>866.1</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>92420.8</v>
-      </c>
-      <c r="O38" s="3" t="inlineStr"/>
+        <v>18.1</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>86.09999999999999</v>
+      </c>
       <c r="P38" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="R38" s="8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S38" s="3" t="inlineStr"/>
-      <c r="T38" s="3" t="inlineStr"/>
-      <c r="U38" s="8" t="n">
-        <v>148.1</v>
+        <v>2.9</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W38" s="3" t="inlineStr"/>
-      <c r="X38" s="3" t="inlineStr"/>
-      <c r="Y38" s="3" t="inlineStr"/>
-      <c r="Z38" s="3" t="n">
-        <v>3931.2</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2872,55 +3614,75 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="H39" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>42.1</v>
+        <v>46.8</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>19.4</v>
+      </c>
       <c r="M39" s="8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="3" t="inlineStr"/>
+        <v>17.5</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>898.6</v>
+      </c>
       <c r="P39" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>26.8</v>
+        <v>41.8</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>26.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="S39" s="3" t="inlineStr"/>
+        <v>40.8</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>92.8</v>
+      </c>
       <c r="T39" s="3" t="n">
-        <v>57.7</v>
+        <v>86.8</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14.9</v>
+        <v>18.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>22</v>
+        <v>29.4</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X39" s="3" t="inlineStr"/>
-      <c r="Y39" s="3" t="inlineStr"/>
+        <v>10.6</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>69.8</v>
+      </c>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -2935,44 +3697,74 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J40" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="K40" s="3" t="inlineStr"/>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="K40" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O40" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="3" t="inlineStr"/>
-      <c r="R40" s="3" t="inlineStr"/>
-      <c r="S40" s="8" t="n">
-        <v>19.8</v>
+      <c r="P40" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>26</v>
+        <v>91.8</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V40" s="3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>20.8</v>
+      </c>
       <c r="W40" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="X40" s="8" t="n">
-        <v>18.6</v>
+      <c r="X40" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>69.2</v>
+        <v>81.5</v>
       </c>
       <c r="Z40" s="3" t="inlineStr"/>
       <c r="AA40" s="3" t="inlineStr">
@@ -2988,42 +3780,74 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="8" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
-      <c r="K41" s="3" t="inlineStr"/>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O41" s="3" t="n">
-        <v>840.1</v>
+        <v>81</v>
       </c>
       <c r="P41" s="3" t="inlineStr"/>
-      <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="inlineStr"/>
-      <c r="S41" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T41" s="3" t="inlineStr"/>
-      <c r="U41" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="V41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="W41" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="X41" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>14.5</v>
+      </c>
       <c r="Y41" s="3" t="n">
-        <v>242.1</v>
-      </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+        <v>76.5</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3037,36 +3861,74 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="n">
+        <v>6.4</v>
+      </c>
       <c r="J42" s="8" t="n">
-        <v>191.6</v>
-      </c>
-      <c r="K42" s="3" t="inlineStr"/>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="3" t="inlineStr"/>
-      <c r="N42" s="3" t="inlineStr"/>
+        <v>11.6</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="O42" s="3" t="n">
-        <v>8540.1</v>
-      </c>
-      <c r="P42" s="3" t="inlineStr"/>
-      <c r="Q42" s="3" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>28.6</v>
+      </c>
       <c r="R42" s="3" t="n">
         <v>21</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
-      <c r="T42" s="3" t="inlineStr"/>
-      <c r="U42" s="3" t="inlineStr"/>
-      <c r="V42" s="3" t="inlineStr"/>
-      <c r="W42" s="3" t="inlineStr"/>
-      <c r="X42" s="3" t="inlineStr"/>
-      <c r="Y42" s="3" t="inlineStr"/>
-      <c r="Z42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W42" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Y42" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>19.8</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3081,39 +3943,75 @@
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>18.5</v>
+      </c>
       <c r="H43" s="8" t="n">
-        <v>172.2</v>
-      </c>
-      <c r="I43" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J43" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="N43" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="O43" s="3" t="inlineStr"/>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
+        <v>15.9</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>9.4</v>
+      </c>
       <c r="R43" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="S43" s="3" t="inlineStr"/>
-      <c r="T43" s="3" t="inlineStr"/>
-      <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
-      <c r="X43" s="3" t="inlineStr"/>
+        <v>29.6</v>
+      </c>
+      <c r="S43" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y43" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z43" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -3128,36 +4026,42 @@
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="n">
-        <v>90</v>
+      <c r="D44" s="8" t="n">
+        <v>18.1</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr"/>
+        <v>16.4</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="H44" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I44" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="N44" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="N44" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="O44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="n">
+        <v>80.8</v>
+      </c>
       <c r="P44" s="3" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>30.6</v>
@@ -3165,14 +4069,24 @@
       <c r="R44" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="S44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="n">
+        <v>20.9</v>
+      </c>
       <c r="T44" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
-      <c r="X44" s="3" t="inlineStr"/>
+      <c r="U44" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W44" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="Y44" s="3" t="n">
         <v>14.8</v>
       </c>
@@ -3190,52 +4104,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="12" t="inlineStr"/>
-      <c r="E45" s="12" t="inlineStr"/>
-      <c r="F45" s="12" t="inlineStr"/>
+      <c r="C45" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>288.4</v>
+      </c>
       <c r="G45" s="3" t="n">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>33.5</v>
+        <v>22</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>61.8</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>9.4</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>109.6</v>
+        <v>1189.6</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="N45" s="3" t="inlineStr"/>
-      <c r="O45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="n">
+        <v>1102.7</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>17992.6</v>
+      </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1656</v>
-      </c>
-      <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr"/>
+        <v>1662</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T45" s="3" t="n">
-        <v>17.9</v>
+        <v>217.9</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>107.1</v>
       </c>
-      <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
+      <c r="V45" s="3" t="n">
+        <v>192.8</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>322.8</v>
+      </c>
       <c r="Y45" s="3" t="n">
-        <v>169.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -3252,21 +4188,23 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="8" t="n">
-        <v>22.8</v>
+      <c r="D46" s="10" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>22.5</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>10.2</v>
@@ -3275,32 +4213,44 @@
       <c r="L46" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
+      <c r="M46" s="8" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>17.5</v>
+      </c>
       <c r="O46" s="3" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="n">
+        <v>27.6</v>
+      </c>
       <c r="R46" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="8" t="n">
+      <c r="S46" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="U46" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="n">
+        <v>23.8</v>
+      </c>
       <c r="W46" s="3" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>69.8</v>
+        <v>19.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>10.7</v>
+        <v>119.4</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,10 +161,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -771,13 +783,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>5.4</v>
-      </c>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="12" t="n">
         <v>18.2</v>
       </c>
       <c r="F4" s="3" t="n">
@@ -787,7 +797,7 @@
         <v>9.6</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>6.8</v>
@@ -798,9 +808,11 @@
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="8" t="n">
-        <v>16.8</v>
+      <c r="L4" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>6.8</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>18.1</v>
@@ -809,16 +821,16 @@
         <v>84</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>513.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>28.5</v>
+        <v>20.5</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>54.8</v>
@@ -848,7 +860,7 @@
       <c r="D5" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="F5" s="3" t="n">
@@ -869,11 +881,11 @@
       <c r="K5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L5" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>128.9</v>
+      <c r="L5" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>16.9</v>
@@ -881,9 +893,7 @@
       <c r="O5" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="P5" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
         <v>28.4</v>
       </c>
@@ -894,7 +904,7 @@
         <v>21.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>56.8</v>
+        <v>58</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>16.8</v>
@@ -902,14 +912,14 @@
       <c r="V5" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>56.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>13.6</v>
@@ -929,12 +939,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E6" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="3" t="n">
         <v>4.5</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -953,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>10.4</v>
+        <v>18.4</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>16.8</v>
@@ -965,7 +975,7 @@
         <v>86</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>28.6</v>
@@ -977,7 +987,7 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>656.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
@@ -1014,12 +1024,10 @@
       <c r="D7" s="3" t="n">
         <v>30.4</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>24.1</v>
-      </c>
+      <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="n">
         <v>12.6</v>
       </c>
@@ -1030,16 +1038,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14.5</v>
+        <v>14.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>118.6</v>
+        <v>18.6</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>484.1</v>
+        <v>7.4</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>19.2</v>
@@ -1047,7 +1055,9 @@
       <c r="O7" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="P7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="Q7" s="3" t="n">
         <v>30.4</v>
       </c>
@@ -1058,25 +1068,25 @@
         <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>142.6</v>
+        <v>42.6</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>19</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>26.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.9</v>
+        <v>19.2</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>81.8</v>
+        <v>27.8</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>14</v>
+        <v>14.9</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1093,26 +1103,26 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E8" s="11" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>19.4</v>
+      <c r="H8" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>15.1</v>
+        <v>1.1</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="n">
@@ -1135,12 +1145,12 @@
         <v>19.7</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>45</v>
+        <v>45.9</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="V8" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="W8" s="3" t="n">
@@ -1173,20 +1183,18 @@
       <c r="E9" s="10" t="n">
         <v>88.7</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>115.2</v>
-      </c>
+      <c r="F9" s="13" t="inlineStr"/>
       <c r="G9" s="3" t="n">
-        <v>57.1</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.6</v>
+        <v>34</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>26.6</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>18.6</v>
@@ -1195,46 +1203,46 @@
         <v>91.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>89.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>42.3</v>
+        <v>423.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>142.8</v>
+        <v>192.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>106</v>
+        <v>186</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>100.8</v>
+        <v>102.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2099.1</v>
+        <v>263.1</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>992.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>12.7</v>
+        <v>127.2</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>11.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>19.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>229.9</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>615</v>
+        <v>68</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1253,17 +1261,17 @@
       <c r="D10" s="10" t="n">
         <v>29.2</v>
       </c>
-      <c r="E10" s="10" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>13.4</v>
+      <c r="E10" s="12" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>11.3</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>6.9</v>
@@ -1272,10 +1280,10 @@
         <v>11.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.5</v>
+        <v>51.1</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>16.6</v>
@@ -1287,7 +1295,7 @@
         <v>84.7</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>29.2</v>
@@ -1299,7 +1307,7 @@
         <v>20.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
@@ -1314,7 +1322,7 @@
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>13.9</v>
@@ -1333,23 +1341,23 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="12" t="n">
-        <v>28.4</v>
+      <c r="D11" s="9" t="n">
+        <v>3.5</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>16.8</v>
+        <v>46.5</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>11.6</v>
+        <v>41.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>5.4</v>
+        <v>54.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1360,20 +1368,20 @@
       <c r="L11" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>1.8</v>
+      <c r="M11" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>890.9</v>
+        <v>82</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q11" s="8" t="n">
-        <v>18.9</v>
+      <c r="Q11" s="3" t="n">
+        <v>28.9</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>20</v>
@@ -1382,7 +1390,7 @@
         <v>18.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1.8</v>
+        <v>47.5</v>
       </c>
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr"/>
@@ -1403,11 +1411,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>28.2</v>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>18</v>
@@ -1437,7 +1443,7 @@
         <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>19.2</v>
+        <v>1.9</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>89</v>
@@ -1446,16 +1452,16 @@
         <v>2.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="R12" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>31</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="n">
@@ -1464,14 +1470,14 @@
       <c r="W12" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="X12" s="8" t="n">
-        <v>97.09999999999999</v>
+      <c r="X12" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>19.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1486,14 +1492,12 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>1.7</v>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>21.6</v>
@@ -1502,7 +1506,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>41.2</v>
+        <v>17.4</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>6</v>
@@ -1511,22 +1515,22 @@
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>283.5</v>
+        <v>23.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>41.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>26</v>
@@ -1535,15 +1539,15 @@
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>51.1</v>
+        <v>57.1</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V13" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1553,11 +1557,9 @@
         <v>19.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z13" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>764</v>
+      </c>
+      <c r="Z13" s="3" t="inlineStr"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1572,25 +1574,23 @@
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="3" t="n">
         <v>27.4</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
+      <c r="F14" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="n">
-        <v>27.8</v>
+        <v>47.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="3" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
@@ -1602,8 +1602,8 @@
       <c r="M14" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>87.8</v>
+      <c r="N14" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>74.5</v>
@@ -1611,32 +1611,32 @@
       <c r="P14" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="Q14" s="8" t="n">
-        <v>86.8</v>
+      <c r="Q14" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>58</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>14</v>
+        <v>14.9</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>3.4</v>
+        <v>17.4</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>10.6</v>
@@ -1655,14 +1655,14 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>23</v>
+      <c r="F15" s="9" t="n">
+        <v>83.8</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11</v>
@@ -1677,8 +1677,8 @@
         <v>10.2</v>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="8" t="n">
-        <v>18.6</v>
+      <c r="L15" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>16.8</v>
@@ -1687,10 +1687,10 @@
         <v>18.1</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>84</v>
+        <v>8.4</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
@@ -1737,11 +1737,9 @@
       </c>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="10" t="n">
-        <v>1198.8</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>90.90000000000001</v>
-      </c>
+        <v>1038.8</v>
+      </c>
+      <c r="E16" s="13" t="inlineStr"/>
       <c r="F16" s="10" t="n">
         <v>1113.9</v>
       </c>
@@ -1749,40 +1747,38 @@
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>22</v>
+        <v>3019.1</v>
       </c>
       <c r="I16" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>90.59999999999999</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>900.6</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>980.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>90.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>920</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>118.2</v>
-      </c>
+        <v>5.7</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
       <c r="Q16" s="3" t="n">
-        <v>2281.2</v>
+        <v>838.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>104.1</v>
+        <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>266.2</v>
@@ -1791,19 +1787,19 @@
         <v>86.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>152.8</v>
+        <v>122.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>94.5</v>
+        <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>92.3</v>
+        <v>93.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>304.8</v>
+        <v>102</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>14.1</v>
+        <v>61</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1818,13 +1814,11 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="E17" s="10" t="n">
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="10" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="F17" s="10" t="n">
@@ -1834,7 +1828,7 @@
         <v>0.1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>16.8</v>
+        <v>26.8</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>6.1</v>
@@ -1846,23 +1840,23 @@
       <c r="L17" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>84</v>
+        <v>8.4</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>13.8</v>
@@ -1871,19 +1865,19 @@
         <v>52.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>17.8</v>
+        <v>1.7</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>18.7</v>
+        <v>0.1</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>12.2</v>
@@ -1901,56 +1895,52 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>24.1</v>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E18" s="14" t="inlineStr"/>
+      <c r="F18" s="3" t="n">
+        <v>8.4</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H18" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <v>12.6</v>
+      <c r="J18" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>62.1</v>
+        <v>18.6</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>14.6</v>
+        <v>78.8</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>21.8</v>
+        <v>30.4</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>29.8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>48.8</v>
@@ -1959,7 +1949,7 @@
         <v>22.2</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>26.4</v>
+        <v>46.4</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.2</v>
@@ -1982,7 +1972,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D19" s="3" t="n">
         <v>29.6</v>
       </c>
@@ -1992,11 +1984,11 @@
       <c r="F19" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G19" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>6.8</v>
@@ -2005,23 +1997,23 @@
         <v>11.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>87</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="P19" s="3" t="inlineStr"/>
       <c r="Q19" s="3" t="n">
-        <v>29.6</v>
+        <v>23.6</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>20.8</v>
@@ -2030,13 +2022,13 @@
         <v>19.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>46.8</v>
+        <v>96.8</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.1</v>
+        <v>26.9</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>19.8</v>
@@ -2045,10 +2037,10 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>19.9</v>
+        <v>14.5</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2065,7 +2057,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="n">
-        <v>18.6</v>
+        <v>10.6</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>18.2</v>
@@ -2078,19 +2070,19 @@
         <v>17.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>117.4</v>
+      <c r="M20" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>19</v>
@@ -2114,7 +2106,7 @@
         <v>48.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>26.4</v>
@@ -2126,7 +2118,7 @@
         <v>20</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>58</v>
+        <v>58.8</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>14.4</v>
@@ -2146,13 +2138,13 @@
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="n">
-        <v>26.8</v>
+        <v>16.6</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>22.3</v>
+      <c r="F21" s="9" t="n">
+        <v>2.2</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>8.6</v>
@@ -2164,19 +2156,19 @@
         <v>6.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>81</v>
@@ -2192,10 +2184,10 @@
         <v>19.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>26</v>
+        <v>256</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15</v>
+        <v>15.9</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.4</v>
@@ -2203,11 +2195,11 @@
       <c r="W21" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="X21" s="8" t="n">
-        <v>18.8</v>
+      <c r="X21" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2227,13 +2219,13 @@
       </c>
       <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>17.6</v>
+        <v>28.4</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>1.7</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>10.8</v>
@@ -2272,7 +2264,7 @@
         <v>19</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>19.5</v>
+        <v>1.9</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>68.3</v>
@@ -2280,15 +2272,17 @@
       <c r="U22" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="W22" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X22" s="3" t="inlineStr"/>
+      <c r="X22" s="3" t="n">
+        <v>155.1</v>
+      </c>
       <c r="Y22" s="3" t="n">
-        <v>16.8</v>
+        <v>16</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>5.7</v>
@@ -2306,77 +2300,75 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="10" t="n">
-        <v>195.6</v>
+        <v>19.6</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>11.1</v>
+        <v>117.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>26.2</v>
+        <v>25.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>529.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>52.9</v>
+        <v>22.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>22</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>88</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.1</v>
+        <v>12</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>926.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>140.4</v>
+        <v>44</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>103.4</v>
+        <v>103.9</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1180.4</v>
+        <v>100.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>267.9</v>
+        <v>8267.799999999999</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>123.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>20.6</v>
+        <v>25.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>41.8</v>
+        <v>94.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>2216.1</v>
+        <v>205.4</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>24.8</v>
+        <v>22.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2391,9 +2383,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C24" s="3" t="inlineStr"/>
       <c r="D24" s="10" t="n">
         <v>29.1</v>
       </c>
@@ -2401,13 +2391,13 @@
         <v>17.9</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>12.1</v>
+        <v>37.5</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2415,7 +2405,9 @@
       <c r="J24" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>5.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>18.6</v>
       </c>
@@ -2444,7 +2436,7 @@
         <v>53.5</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>24.7</v>
@@ -2453,7 +2445,7 @@
         <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.9</v>
+        <v>12.9</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>61</v>
@@ -2474,66 +2466,62 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>81.5</v>
-      </c>
+      <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>23</v>
+        <v>12.8</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>2.3</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>20.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>56.9</v>
+        <v>10.8</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>221.8</v>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
       <c r="R25" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>20.9</v>
+        <v>662.3</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="W25" s="8" t="n">
-        <v>86.40000000000001</v>
+        <v>19.8</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
       <c r="Y25" s="3" t="inlineStr"/>
@@ -2552,28 +2540,28 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="E26" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G26" s="8" t="n">
-        <v>10.2</v>
+      <c r="E26" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
@@ -2584,11 +2572,9 @@
       <c r="M26" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>48.4</v>
-      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>69.8</v>
+        <v>6</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>3</v>
@@ -2606,10 +2592,10 @@
         <v>12.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>29.4</v>
+        <v>43.8</v>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v>49.4</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>18.6</v>
@@ -2618,10 +2604,10 @@
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>38.5</v>
+        <v>18.6</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>112.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2637,31 +2623,31 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>17.2</v>
+        <v>12.7</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>7.2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>22.8</v>
+        <v>12.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>6.9</v>
+        <v>68.7</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.1</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
@@ -2669,16 +2655,18 @@
       <c r="M27" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="N27" s="8" t="n">
-        <v>21.8</v>
+      <c r="N27" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>188.9</v>
+        <v>22.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="n">
+        <v>4.1</v>
+      </c>
       <c r="R27" s="3" t="n">
         <v>20.8</v>
       </c>
@@ -2686,7 +2674,7 @@
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>56.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>12.8</v>
@@ -2716,13 +2704,15 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F28" s="11" t="inlineStr"/>
+      <c r="D28" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>1.7</v>
+      </c>
       <c r="G28" s="3" t="n">
         <v>9.4</v>
       </c>
@@ -2741,25 +2731,25 @@
       <c r="L28" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="M28" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>17.8</v>
+      <c r="M28" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>5294</v>
+        <v>0</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>21.4</v>
+        <v>27.4</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S28" s="8" t="n">
+      <c r="S28" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T28" s="3" t="n">
@@ -2794,9 +2784,9 @@
       </c>
       <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E29" s="12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="F29" s="3" t="n">
@@ -2839,13 +2829,13 @@
         <v>19.8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>659.5</v>
+        <v>1.8</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>13.2</v>
+        <v>152.5</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>23.6</v>
@@ -2853,8 +2843,8 @@
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>12.8</v>
+      <c r="X29" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2875,27 +2865,29 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="D30" s="10" t="n">
-        <v>1952.4</v>
+        <v>1334.8</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>80.8</v>
+        <v>85.8</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1816.8</v>
+        <v>109.8</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>47.4</v>
+        <v>48.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2016.1</v>
+        <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2681.4</v>
+        <v>32.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>90.40000000000001</v>
@@ -2904,22 +2896,22 @@
         <v>91.40000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>836.5</v>
+        <v>185.4</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>19</v>
+        <v>904.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>420</v>
+        <v>43464.4</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>12.2</v>
+        <v>15.2</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>132</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1082</v>
+        <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>102.2</v>
@@ -2928,22 +2920,22 @@
         <v>298.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>10</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1818.2</v>
+        <v>118.2</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>985.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>418.1</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>316.2</v>
+        <v>3136.2</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>49.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2959,12 +2951,12 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="D31" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="10" t="n">
         <v>17.2</v>
       </c>
       <c r="F31" s="10" t="n">
@@ -2977,14 +2969,16 @@
         <v>26.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>85.2</v>
+      </c>
       <c r="L31" s="8" t="n">
-        <v>318.3</v>
+        <v>18.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>16.7</v>
@@ -3023,7 +3017,7 @@
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>69.2</v>
+        <v>475.1</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>10</v>
@@ -3041,20 +3035,16 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="9" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>18.9</v>
+        <v>0.9</v>
+      </c>
+      <c r="E32" s="14" t="inlineStr"/>
+      <c r="F32" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>15.2</v>
@@ -3078,37 +3068,37 @@
         <v>18.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>86.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="R32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R32" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="V32" s="8" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
@@ -3124,14 +3114,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>18</v>
+        <v>8.6</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>23.1</v>
@@ -3143,10 +3131,10 @@
         <v>17.2</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -3155,21 +3143,21 @@
         <v>17.4</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>15.6</v>
+        <v>1.5</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>16.7</v>
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>84</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="R33" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="R33" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3184,7 +3172,7 @@
       <c r="V33" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3209,15 +3197,15 @@
       </c>
       <c r="C34" s="3" t="inlineStr"/>
       <c r="D34" s="3" t="n">
-        <v>24.2</v>
+        <v>10.8</v>
       </c>
       <c r="E34" s="9" t="n">
         <v>1.7</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="G34" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G34" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3242,15 +3230,15 @@
         <v>18.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="R34" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3262,14 +3250,14 @@
       <c r="U34" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="V34" s="8" t="n">
-        <v>284.6</v>
+      <c r="V34" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>20.1</v>
+        <v>20.7</v>
       </c>
       <c r="Y34" s="3" t="inlineStr"/>
       <c r="Z34" s="3" t="inlineStr"/>
@@ -3287,7 +3275,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>28.6</v>
@@ -3295,8 +3283,8 @@
       <c r="E35" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>21.8</v>
+      <c r="F35" s="9" t="n">
+        <v>3.2</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>10.8</v>
@@ -3304,8 +3292,8 @@
       <c r="H35" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="I35" s="8" t="n">
-        <v>11</v>
+      <c r="I35" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>5.2</v>
@@ -3323,16 +3311,16 @@
         <v>16.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="P35" s="8" t="n">
-        <v>12.9</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>190.8</v>
+        <v>19</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.9</v>
@@ -3346,7 +3334,7 @@
       <c r="V35" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="8" t="n">
+      <c r="W35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3367,17 +3355,15 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D36" s="9" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>17.8</v>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>22.2</v>
+        <v>12.2</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>10.8</v>
@@ -3386,7 +3372,7 @@
         <v>16.8</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>8</v>
@@ -3398,7 +3384,7 @@
         <v>18.6</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>18.8</v>
@@ -3422,7 +3408,7 @@
         <v>26.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>460.8</v>
+        <v>17</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.4</v>
@@ -3452,73 +3438,73 @@
       </c>
       <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="10" t="n">
-        <v>1120.8</v>
+        <v>1138.8</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>80.2</v>
+        <v>88.2</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>111</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>498.6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>808</v>
+        <v>898</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>21816.4</v>
+        <v>210.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>219.8</v>
+        <v>31.8</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>118.2</v>
+        <v>1.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>11.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>1082.2</v>
+        <v>82.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>4920.8</v>
+        <v>12.6</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>14.9</v>
+        <v>44.5</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>1102.2</v>
+        <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>101.9</v>
+        <v>10.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>288.6</v>
+        <v>208.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>14.1</v>
+        <v>44.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>109.8</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>106.8</v>
+        <v>156</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>231.2</v>
+        <v>31.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3553,15 +3539,15 @@
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3580,16 +3566,16 @@
         <v>20.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>28.3</v>
+        <v>88.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>38.7</v>
+        <v>57.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>22</v>
+        <v>240.1</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>19</v>
@@ -3614,74 +3600,70 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="C39" s="3" t="inlineStr"/>
       <c r="D39" s="3" t="n">
-        <v>26</v>
+        <v>26.6</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>2.6</v>
+        <v>43.6</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>46.8</v>
+        <v>4.8</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>36.1</v>
+        <v>3.8</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>19</v>
+      <c r="M39" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>898.6</v>
+        <v>8.4</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="Q39" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>40.8</v>
-      </c>
+      <c r="R39" s="3" t="inlineStr"/>
       <c r="S39" s="8" t="n">
-        <v>92.8</v>
+        <v>19.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>86.8</v>
+        <v>26</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>29.4</v>
+        <v>23.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>10.6</v>
+        <v>18.6</v>
       </c>
       <c r="X39" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>69.8</v>
+        <v>64.2</v>
       </c>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
@@ -3698,31 +3680,29 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>26.2</v>
+        <v>16.2</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>16.4</v>
+        <v>22.8</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>8.4</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J40" s="3" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>19.2</v>
@@ -3737,19 +3717,19 @@
         <v>84</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>26.2</v>
+        <v>16.2</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>91.8</v>
+        <v>51.8</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>14.4</v>
@@ -3781,10 +3761,10 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>18.4</v>
@@ -3793,28 +3773,28 @@
         <v>21.9</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.5</v>
+        <v>43.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>18.9</v>
+        <v>1.7</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
@@ -3826,12 +3806,14 @@
       <c r="R41" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S41" s="3" t="inlineStr"/>
+      <c r="S41" s="3" t="n">
+        <v>17.2</v>
+      </c>
       <c r="T41" s="3" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v>108.4</v>
+        <v>62.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>19.6</v>
@@ -3840,7 +3822,7 @@
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>76.5</v>
@@ -3861,9 +3843,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C42" s="3" t="inlineStr"/>
       <c r="D42" s="3" t="n">
         <v>30.4</v>
       </c>
@@ -3871,18 +3851,18 @@
         <v>16</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="H42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="n">
+        <v>14</v>
+      </c>
       <c r="I42" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="J42" s="3" t="inlineStr"/>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
@@ -3893,7 +3873,7 @@
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>12</v>
+        <v>17.8</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>85</v>
@@ -3905,7 +3885,7 @@
         <v>28.6</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
       <c r="T42" s="3" t="n">
@@ -3917,17 +3897,17 @@
       <c r="V42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W42" s="8" t="n">
+      <c r="W42" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X42" s="8" t="n">
+      <c r="X42" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>57</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3944,22 +3924,20 @@
       </c>
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="n">
-        <v>30.4</v>
+        <v>10.4</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>22.7</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="F43" s="14" t="inlineStr"/>
       <c r="G43" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>17.2</v>
+        <v>19.2</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>15</v>
@@ -3982,25 +3960,25 @@
       <c r="P43" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q43" s="8" t="n">
-        <v>9.4</v>
+      <c r="Q43" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="S43" s="8" t="n">
-        <v>18</v>
+      <c r="S43" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>29.9</v>
+        <v>92.59999999999999</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W43" s="8" t="n">
+      <c r="W43" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4025,15 +4003,17 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="E44" s="3" t="n">
+      <c r="C44" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>80</v>
+        <v>21.7</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>14.2</v>
@@ -4042,17 +4022,19 @@
         <v>15.8</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr"/>
+        <v>7.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K44" s="3" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M44" s="8" t="n">
-        <v>26.5</v>
+      <c r="M44" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="N44" s="8" t="n">
         <v>16.4</v>
@@ -4061,7 +4043,7 @@
         <v>80.8</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>30.6</v>
@@ -4075,14 +4057,12 @@
       <c r="T44" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U44" s="8" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="U44" s="3" t="inlineStr"/>
       <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W44" s="8" t="n">
-        <v>20.8</v>
+      <c r="W44" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4104,56 +4084,52 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="10" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>288.4</v>
+        <v>830.6</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>92.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>22</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.8</v>
+        <v>61</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1189.6</v>
+        <v>1089.6</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1102.7</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>17992.6</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="O45" s="3" t="inlineStr"/>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1662</v>
+        <v>650.2</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>121</v>
+        <v>1.3</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>11.6</v>
+        <v>746.4</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>217.9</v>
@@ -4162,13 +4138,13 @@
         <v>107.1</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>192.8</v>
+        <v>12.8</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>112</v>
+        <v>114.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>322.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>64.40000000000001</v>
@@ -4189,22 +4165,22 @@
       </c>
       <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="10" t="n">
-        <v>71.90000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>17.1</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>19.4</v>
+        <v>15.4</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>10.2</v>
@@ -4213,11 +4189,11 @@
       <c r="L46" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>85.40000000000001</v>
+      <c r="M46" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>83.09999999999999</v>
@@ -4226,19 +4202,19 @@
         <v>3.6</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>23</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>18.8</v>
+        <v>17.8</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>23.8</v>
@@ -4250,7 +4226,7 @@
         <v>19.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>119.4</v>
+        <v>165.4</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -808,7 +808,7 @@
       <c r="K4" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="9" t="n">
         <v>1.8</v>
       </c>
       <c r="M4" s="3" t="n">
@@ -823,10 +823,10 @@
       <c r="P4" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="12" t="n">
         <v>27.8</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="12" t="n">
         <v>20.8</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -838,8 +838,8 @@
       <c r="U4" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V4" s="3" t="inlineStr"/>
-      <c r="W4" s="3" t="inlineStr"/>
+      <c r="V4" s="14" t="inlineStr"/>
+      <c r="W4" s="12" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -894,10 +894,10 @@
         <v>83</v>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="12" t="n">
         <v>28.4</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="12" t="n">
         <v>21.6</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -912,7 +912,7 @@
       <c r="V5" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -977,10 +977,10 @@
       <c r="P6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="12" t="n">
         <v>28.6</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="12" t="n">
         <v>21.8</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -995,7 +995,7 @@
       <c r="V6" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="12" t="n">
         <v>20</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1058,10 +1058,10 @@
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="12" t="n">
         <v>30.4</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="12" t="n">
         <v>20.6</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1073,10 +1073,10 @@
       <c r="U7" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="12" t="n">
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1124,7 +1124,7 @@
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr"/>
       <c r="M8" s="3" t="n">
         <v>16.4</v>
       </c>
@@ -1135,10 +1135,10 @@
         <v>81</v>
       </c>
       <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="12" t="n">
         <v>30.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1153,7 +1153,7 @@
       <c r="V8" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="12" t="n">
         <v>19.4</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1196,13 +1196,13 @@
       <c r="J9" s="3" t="n">
         <v>86.40000000000001</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="10" t="n">
         <v>91.7</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="10" t="n">
         <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1214,10 +1214,10 @@
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="10" t="n">
         <v>192.8</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="10" t="n">
         <v>186</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1229,10 +1229,10 @@
       <c r="U9" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="10" t="n">
         <v>127.2</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="10" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1282,10 +1282,10 @@
       <c r="K10" s="3" t="n">
         <v>51.1</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="10" t="n">
         <v>16.6</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1297,10 +1297,10 @@
       <c r="P10" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="12" t="n">
         <v>29.2</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1312,10 +1312,10 @@
       <c r="U10" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="10" t="n">
         <v>25.4</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="12" t="n">
         <v>19.5</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1383,7 +1383,7 @@
       <c r="Q11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="12" t="n">
         <v>20</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1393,8 +1393,8 @@
         <v>47.5</v>
       </c>
       <c r="U11" s="3" t="inlineStr"/>
-      <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
+      <c r="V11" s="12" t="inlineStr"/>
+      <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
       <c r="P12" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="12" t="n">
         <v>21.6</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1464,10 +1464,10 @@
         <v>31</v>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="12" t="n">
         <v>25.6</v>
       </c>
-      <c r="W12" s="8" t="n">
+      <c r="W12" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1535,7 +1535,7 @@
       <c r="Q13" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="12" t="n">
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1547,10 +1547,10 @@
       <c r="U13" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="12" t="n">
         <v>25.6</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1614,7 +1614,7 @@
       <c r="Q14" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" s="12" t="n">
         <v>19.9</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1626,10 +1626,10 @@
       <c r="U14" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1676,7 +1676,7 @@
       <c r="J15" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K15" s="3" t="inlineStr"/>
+      <c r="K15" s="14" t="inlineStr"/>
       <c r="L15" s="3" t="n">
         <v>11.8</v>
       </c>
@@ -1695,7 +1695,7 @@
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1707,10 +1707,10 @@
       <c r="U15" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="12" t="n">
         <v>25.4</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1755,13 +1755,13 @@
       <c r="J16" s="3" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="10" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1771,10 +1771,10 @@
         <v>5.7</v>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="10" t="n">
         <v>838.2</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="10" t="n">
         <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1786,10 +1786,10 @@
       <c r="U16" s="3" t="n">
         <v>86.2</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="10" t="n">
         <v>122.8</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="10" t="n">
         <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1837,10 +1837,10 @@
         <v>10.1</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1852,10 +1852,10 @@
       <c r="P17" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="10" t="n">
         <v>27.6</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="12" t="n">
         <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1867,10 +1867,10 @@
       <c r="U17" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="12" t="n">
         <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1921,7 +1921,7 @@
       <c r="L18" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1948,10 +1948,10 @@
       <c r="U18" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="9" t="n">
         <v>46.4</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="12" t="n">
         <v>20.2</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2002,7 +2002,7 @@
       <c r="L19" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="12" t="n">
         <v>17.2</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2030,7 +2030,7 @@
       <c r="V19" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2081,7 +2081,7 @@
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2111,7 +2111,7 @@
       <c r="V20" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="12" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2161,10 +2161,10 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2176,7 +2176,7 @@
       <c r="P21" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="Q21" s="14" t="inlineStr"/>
       <c r="R21" s="3" t="n">
         <v>20</v>
       </c>
@@ -2192,7 +2192,7 @@
       <c r="V21" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="W21" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2245,7 +2245,7 @@
       <c r="L22" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
@@ -2275,7 +2275,7 @@
       <c r="V22" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2322,13 +2322,13 @@
       <c r="J23" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="10" t="n">
         <v>88</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2340,10 +2340,10 @@
       <c r="P23" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="10" t="n">
         <v>103.9</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2355,10 +2355,10 @@
       <c r="U23" s="3" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="10" t="n">
         <v>123.5</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="10" t="n">
         <v>25.6</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2408,10 +2408,10 @@
       <c r="K24" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="12" t="n">
         <v>17</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2423,10 +2423,10 @@
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="10" t="n">
         <v>28.1</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="10" t="n">
         <v>20.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2438,10 +2438,10 @@
       <c r="U24" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2506,8 +2506,8 @@
       <c r="P25" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="Q25" s="3" t="inlineStr"/>
-      <c r="R25" s="3" t="n">
+      <c r="Q25" s="14" t="inlineStr"/>
+      <c r="R25" s="12" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2520,7 +2520,7 @@
       <c r="V25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="12" t="n">
         <v>18.4</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
@@ -2582,7 +2582,7 @@
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2594,10 +2594,10 @@
       <c r="U26" s="3" t="n">
         <v>43.8</v>
       </c>
-      <c r="V26" s="8" t="n">
+      <c r="V26" s="9" t="n">
         <v>49.4</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2664,10 +2664,10 @@
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="12" t="n">
         <v>20.8</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2682,7 +2682,7 @@
       <c r="V27" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2746,7 +2746,7 @@
       <c r="Q28" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="12" t="n">
         <v>20.8</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2761,7 +2761,7 @@
       <c r="V28" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2825,7 +2825,7 @@
       <c r="Q29" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2840,7 +2840,7 @@
       <c r="V29" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="12" t="n">
         <v>19</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2889,13 +2889,13 @@
       <c r="J30" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="10" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="10" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="10" t="n">
         <v>185.4</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2907,10 +2907,10 @@
       <c r="P30" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="10" t="n">
         <v>132</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="12" t="n">
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -2922,10 +2922,10 @@
       <c r="U30" s="3" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="10" t="n">
         <v>118.2</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="10" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -2977,10 +2977,10 @@
       <c r="K31" s="3" t="n">
         <v>85.2</v>
       </c>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="10" t="n">
         <v>18.3</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="10" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -2992,10 +2992,10 @@
       <c r="P31" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="10" t="n">
         <v>26.4</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="12" t="n">
         <v>20.4</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3007,10 +3007,10 @@
       <c r="U31" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3058,7 +3058,7 @@
       <c r="K32" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="12" t="n">
         <v>18.4</v>
       </c>
       <c r="M32" s="3" t="n">
@@ -3076,7 +3076,7 @@
       <c r="Q32" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3088,10 +3088,10 @@
       <c r="U32" s="8" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3139,10 +3139,10 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3157,7 +3157,7 @@
       <c r="Q33" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="12" t="n">
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3169,10 +3169,10 @@
       <c r="U33" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3220,7 +3220,7 @@
       <c r="K34" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="12" t="n">
         <v>18.4</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3238,7 +3238,7 @@
       <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="12" t="n">
         <v>21.6</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3250,10 +3250,10 @@
       <c r="U34" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="12" t="n">
         <v>20</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3301,7 +3301,7 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="M35" s="3" t="n">
@@ -3316,10 +3316,10 @@
       <c r="P35" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="12" t="n">
         <v>19</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3331,10 +3331,10 @@
       <c r="U35" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3380,7 +3380,7 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="M36" s="3" t="n">
@@ -3398,7 +3398,7 @@
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="12" t="n">
         <v>21.8</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3410,10 +3410,10 @@
       <c r="U36" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3458,13 +3458,13 @@
       <c r="J37" s="3" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="12" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="10" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3476,10 +3476,10 @@
       <c r="P37" s="3" t="n">
         <v>44.5</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="10" t="n">
         <v>132.8</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="12" t="n">
         <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3491,10 +3491,10 @@
       <c r="U37" s="3" t="n">
         <v>44.7</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="12" t="n">
         <v>109.8</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="10" t="n">
         <v>18.4</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3544,10 +3544,10 @@
       <c r="K38" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="12" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="10" t="n">
         <v>16.5</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3559,10 +3559,10 @@
       <c r="P38" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="12" t="n">
         <v>20.4</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3574,10 +3574,10 @@
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="10" t="n">
         <v>240.1</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="12" t="n">
         <v>19</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3625,7 +3625,7 @@
       <c r="K39" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="L39" s="8" t="n">
+      <c r="L39" s="12" t="n">
         <v>19.4</v>
       </c>
       <c r="M39" s="3" t="n">
@@ -3643,7 +3643,7 @@
       <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="inlineStr"/>
+      <c r="R39" s="14" t="inlineStr"/>
       <c r="S39" s="8" t="n">
         <v>19.8</v>
       </c>
@@ -3653,7 +3653,7 @@
       <c r="U39" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="12" t="n">
         <v>23.9</v>
       </c>
       <c r="W39" s="3" t="n">
@@ -3704,7 +3704,7 @@
       <c r="K40" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="12" t="n">
         <v>19.2</v>
       </c>
       <c r="M40" s="3" t="n">
@@ -3734,7 +3734,7 @@
       <c r="U40" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="12" t="n">
         <v>20.8</v>
       </c>
       <c r="W40" s="3" t="n">
@@ -3787,10 +3787,10 @@
       <c r="K41" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="12" t="n">
         <v>19.4</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="9" t="n">
         <v>1.7</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3815,7 +3815,7 @@
       <c r="U41" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="12" t="n">
         <v>19.6</v>
       </c>
       <c r="W41" s="3" t="n">
@@ -3866,7 +3866,7 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -3884,7 +3884,7 @@
       <c r="Q42" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="9" t="n">
         <v>4.1</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -3894,7 +3894,7 @@
       <c r="U42" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="12" t="n">
         <v>26.4</v>
       </c>
       <c r="W42" s="3" t="n">
@@ -3945,7 +3945,7 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="12" t="n">
         <v>16.4</v>
       </c>
       <c r="M43" s="3" t="n">
@@ -3975,7 +3975,7 @@
       <c r="U43" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="12" t="n">
         <v>26.4</v>
       </c>
       <c r="W43" s="3" t="n">
@@ -4030,7 +4030,7 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="M44" s="3" t="n">
@@ -4058,7 +4058,7 @@
         <v>47</v>
       </c>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="12" t="n">
         <v>26.4</v>
       </c>
       <c r="W44" s="3" t="n">
@@ -4106,13 +4106,13 @@
       <c r="J45" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="10" t="n">
         <v>9.9</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="10" t="n">
         <v>1089.6</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="10" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4122,10 +4122,10 @@
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="10" t="n">
         <v>650.2</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="10" t="n">
         <v>1.3</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4137,10 +4137,10 @@
       <c r="U45" s="3" t="n">
         <v>107.1</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="10" t="n">
         <v>12.8</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="10" t="n">
         <v>114.8</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4186,10 +4186,10 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="12" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="10" t="n">
         <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4201,10 +4201,10 @@
       <c r="P46" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="10" t="n">
         <v>20.1</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4216,10 +4216,10 @@
       <c r="U46" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="10" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,20 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,8 +59,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,25 +146,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -785,19 +788,19 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="F4" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>18.2</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>6.8</v>
@@ -805,41 +808,39 @@
       <c r="J4" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>6.8</v>
+      <c r="L4" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>86.8</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.1</v>
+        <v>17</v>
       </c>
       <c r="O4" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q4" s="13" t="n">
         <v>84</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q4" s="12" t="n">
+      <c r="R4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="R4" s="12" t="n">
+      <c r="S4" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="T4" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V4" s="14" t="inlineStr"/>
-      <c r="W4" s="12" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="11" t="inlineStr"/>
+      <c r="W4" s="11" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -856,14 +857,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D5" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="11" t="n">
         <v>23</v>
       </c>
       <c r="G5" s="3" t="n">
@@ -878,48 +881,50 @@
       <c r="J5" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="K5" s="3" t="n">
-        <v>0.4</v>
+      <c r="K5" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>18.6</v>
+        <v>17.1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="12" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R5" s="12" t="n">
+      <c r="R5" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>58</v>
+        <v>54.8</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="12" t="n">
+      <c r="W5" s="11" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>5.6</v>
+        <v>56.5</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>13.6</v>
@@ -937,15 +942,17 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E6" s="12" t="n">
+      <c r="C6" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>4.5</v>
+      <c r="F6" s="11" t="n">
+        <v>23.9</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>10.8</v>
@@ -959,7 +966,7 @@
       <c r="J6" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
@@ -972,30 +979,30 @@
         <v>18.2</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>86</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" s="12" t="n">
+      <c r="Q6" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R6" s="12" t="n">
+      <c r="R6" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>58</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V6" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="W6" s="12" t="n">
+      <c r="V6" s="11" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W6" s="11" t="n">
         <v>20</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1020,14 +1027,18 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D7" s="3" t="n">
         <v>30.4</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="F7" s="11" t="n">
+        <v>24.1</v>
+      </c>
       <c r="G7" s="3" t="n">
         <v>12.6</v>
       </c>
@@ -1038,55 +1049,55 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>7.4</v>
+      <c r="L7" s="13" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>17.4</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="12" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="R7" s="12" t="n">
+      <c r="Q7" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>42.6</v>
+        <v>656.4</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="W7" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="V7" s="11" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="W7" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="X7" s="3" t="n">
+      <c r="X7" s="14" t="n">
         <v>19.2</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>14.9</v>
+        <v>14</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1102,31 +1113,35 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E8" s="12" t="inlineStr"/>
-      <c r="F8" s="3" t="n">
-        <v>22.9</v>
+      <c r="D8" s="3" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>23.59</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>15.4</v>
+        <v>19.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="14" t="inlineStr"/>
+      <c r="L8" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="M8" s="3" t="n">
-        <v>16.4</v>
+        <v>17.4</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>17.4</v>
@@ -1134,34 +1149,38 @@
       <c r="O8" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="12" t="n">
+      <c r="P8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="R8" s="12" t="n">
+      <c r="R8" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>45.9</v>
+        <v>42.6</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="W8" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="V8" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="W8" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>19.4</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="n">
-        <v>14.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1177,36 +1196,38 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="10" t="n">
-        <v>142.8</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="F9" s="13" t="inlineStr"/>
+      <c r="D9" s="9" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>887.1</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>17.2</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>27.1</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34</v>
+        <v>34.8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="K9" s="10" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="K9" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L9" s="9" t="n">
         <v>91.7</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="9" t="n">
         <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>423.5</v>
@@ -1214,35 +1235,35 @@
       <c r="P9" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="Q9" s="10" t="n">
-        <v>192.8</v>
-      </c>
-      <c r="R9" s="10" t="n">
-        <v>186</v>
+      <c r="Q9" s="9" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="R9" s="9" t="n">
+        <v>1196</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>102.6</v>
+        <v>182.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>263.1</v>
+        <v>9255.1</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="V9" s="10" t="n">
+      <c r="V9" s="9" t="n">
         <v>127.2</v>
       </c>
-      <c r="W9" s="10" t="n">
-        <v>97.40000000000001</v>
+      <c r="W9" s="9" t="n">
+        <v>971.4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>229.9</v>
+        <v>26.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1258,17 +1279,17 @@
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="11" t="n">
         <v>23.4</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>16.5</v>
@@ -1277,15 +1298,15 @@
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.3</v>
+        <v>1.1</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="L10" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="9" t="n">
         <v>16.6</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1297,35 +1318,35 @@
       <c r="P10" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q10" s="12" t="n">
+      <c r="Q10" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="R10" s="12" t="n">
+      <c r="R10" s="9" t="n">
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>20.5</v>
+        <v>90.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="W10" s="12" t="n">
+      <c r="W10" s="11" t="n">
         <v>19.5</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1341,23 +1362,23 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>46.5</v>
+      <c r="D11" s="11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>76.90000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>13.2</v>
+        <v>1.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>54.6</v>
+        <v>15.4</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1365,38 +1386,48 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="L11" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="14" t="n">
         <v>18.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R11" s="12" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="R11" s="11" t="n">
         <v>20</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>18.4</v>
+        <v>13.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="U11" s="3" t="inlineStr"/>
-      <c r="V11" s="12" t="inlineStr"/>
-      <c r="W11" s="12" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="inlineStr"/>
+        <v>425.4</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="13" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="W11" s="13" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>48.9</v>
+      </c>
       <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1411,15 +1442,17 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="n">
-        <v>18.4</v>
+      <c r="C12" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>28.2</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>23.1</v>
+      <c r="F12" s="13" t="n">
+        <v>43.1</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>10.2</v>
@@ -1436,10 +1469,10 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="14" t="n">
         <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1449,35 +1482,37 @@
         <v>89</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" s="9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Q12" s="13" t="n">
         <v>2.8</v>
       </c>
-      <c r="R12" s="12" t="n">
+      <c r="R12" s="11" t="n">
         <v>21.6</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="12" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="W12" s="12" t="n">
-        <v>19.8</v>
+        <v>257.1</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V12" s="13" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>13.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1493,11 +1528,11 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="n">
-        <v>6</v>
+      <c r="D13" s="11" t="n">
+        <v>26</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>17.2</v>
+        <v>11.2</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>21.6</v>
@@ -1506,7 +1541,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>6</v>
@@ -1515,9 +1550,9 @@
         <v>9.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1527,39 +1562,41 @@
         <v>16.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>23.5</v>
+        <v>83.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="R13" s="12" t="n">
+      <c r="R13" s="11" t="n">
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>57.1</v>
+        <v>58</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V13" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="W13" s="12" t="n">
-        <v>19.8</v>
+      <c r="W13" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>764</v>
-      </c>
-      <c r="Z13" s="3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>13</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1574,7 +1611,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="11" t="n">
         <v>27.4</v>
       </c>
       <c r="E14" s="3" t="n">
@@ -1583,30 +1620,32 @@
       <c r="F14" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="H14" s="3" t="n">
-        <v>47.8</v>
+        <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="14" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="14" t="n">
         <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>74.5</v>
+        <v>714.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>5.8</v>
@@ -1614,29 +1653,29 @@
       <c r="Q14" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="R14" s="12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>19.6</v>
+      <c r="R14" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="S14" s="14" t="n">
+        <v>18.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58</v>
+        <v>51.5</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V14" s="12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W14" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="W14" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>10.6</v>
@@ -1655,14 +1694,14 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="11" t="n">
         <v>28.8</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F15" s="9" t="n">
-        <v>83.8</v>
+      <c r="F15" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11</v>
@@ -1676,9 +1715,11 @@
       <c r="J15" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K15" s="14" t="inlineStr"/>
-      <c r="L15" s="3" t="n">
-        <v>11.8</v>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>18.6</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>16.8</v>
@@ -1687,15 +1728,15 @@
         <v>18.1</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>8.4</v>
+        <v>84</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>13.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R15" s="12" t="n">
+      <c r="R15" s="11" t="n">
         <v>21.2</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1705,22 +1746,22 @@
         <v>52.1</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V15" s="12" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V15" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="W15" s="12" t="n">
-        <v>18.8</v>
+      <c r="W15" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>114.6</v>
+        <v>17.8</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1735,71 +1776,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="10" t="n">
-        <v>1038.8</v>
-      </c>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="10" t="n">
-        <v>1113.9</v>
+      <c r="C16" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>113.9</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3019.1</v>
+        <v>288.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>20.6</v>
+        <v>0.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="K16" s="10" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="M16" s="10" t="n">
+      <c r="L16" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="M16" s="9" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>909.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="10" t="n">
-        <v>838.2</v>
-      </c>
-      <c r="R16" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="Q16" s="9" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="R16" s="11" t="n">
         <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>98.8</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>266.2</v>
+        <v>66.8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>86.2</v>
       </c>
-      <c r="V16" s="10" t="n">
+      <c r="V16" s="9" t="n">
         <v>122.8</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="W16" s="9" t="n">
         <v>94.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>102</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1815,20 +1862,20 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="10" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E17" s="3" t="n">
+      <c r="D17" s="11" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="G17" s="8" t="n">
-        <v>0.1</v>
+      <c r="G17" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>26.8</v>
+        <v>16.8</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>6.1</v>
@@ -1837,50 +1884,50 @@
         <v>10.1</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="10" t="n">
+      <c r="L17" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>18.1</v>
+      <c r="N17" s="14" t="n">
+        <v>19.1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q17" s="10" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="R17" s="12" t="n">
-        <v>20.4</v>
+        <v>3.4</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R17" s="9" t="n">
+        <v>11.4</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>13.8</v>
+        <v>19.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>52.2</v>
+        <v>51.2</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="V17" s="12" t="n">
+      <c r="V17" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="W17" s="12" t="n">
-        <v>19</v>
+      <c r="W17" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>0.1</v>
+        <v>15.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>60.4</v>
+        <v>1068.5</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>12.2</v>
+        <v>810.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1895,70 +1942,78 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D18" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E18" s="14" t="inlineStr"/>
-      <c r="F18" s="3" t="n">
-        <v>8.4</v>
+        <v>30.4</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.1</v>
+        <v>13.6</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>13.6</v>
+        <v>456.1</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>13.6</v>
+        <v>126.1</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="M18" s="11" t="n">
         <v>16.2</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>17.8</v>
+        <v>4.7</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>78.8</v>
+        <v>138.8</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q18" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="R18" s="8" t="n">
-        <v>29.8</v>
+      <c r="Q18" s="13" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="R18" s="13" t="n">
+        <v>44.8</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>48.8</v>
+        <v>457.1</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="V18" s="9" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="W18" s="12" t="n">
-        <v>20.2</v>
+        <v>4.4</v>
+      </c>
+      <c r="V18" s="13" t="n">
+        <v>46.47</v>
+      </c>
+      <c r="W18" s="13" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y18" s="3" t="inlineStr"/>
-      <c r="Z18" s="3" t="inlineStr"/>
+        <v>86</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>38</v>
+      </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1972,9 +2027,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="n">
         <v>29.6</v>
       </c>
@@ -1982,13 +2035,13 @@
         <v>17.8</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>6.8</v>
@@ -1997,23 +2050,25 @@
         <v>11.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="M19" s="11" t="n">
         <v>17.2</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>18.7</v>
+      <c r="N19" s="14" t="n">
+        <v>18.1</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="n">
-        <v>23.6</v>
+        <v>81</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q19" s="13" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>20.8</v>
@@ -2022,7 +2077,7 @@
         <v>19.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>96.8</v>
+        <v>46.8</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>22</v>
@@ -2030,17 +2085,17 @@
       <c r="V19" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="W19" s="12" t="n">
+      <c r="W19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>24</v>
+        <v>294</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2055,7 +2110,9 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D20" s="3" t="n">
         <v>10.6</v>
       </c>
@@ -2065,12 +2122,14 @@
       <c r="F20" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="8" t="n">
-        <v>17.4</v>
+      <c r="G20" s="14" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>12.6</v>
@@ -2081,7 +2140,7 @@
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="M20" s="11" t="n">
         <v>17.4</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2103,25 +2162,25 @@
         <v>20.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>48.8</v>
+        <v>47.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W20" s="12" t="n">
+      <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>20</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>58.8</v>
+        <v>58</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2138,12 +2197,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="n">
-        <v>16.6</v>
+        <v>26.6</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="13" t="n">
         <v>2.2</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2156,19 +2215,19 @@
         <v>6.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M21" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M21" s="11" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>81</v>
@@ -2176,7 +2235,9 @@
       <c r="P21" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q21" s="14" t="inlineStr"/>
+      <c r="Q21" s="3" t="n">
+        <v>26.6</v>
+      </c>
       <c r="R21" s="3" t="n">
         <v>20</v>
       </c>
@@ -2184,22 +2245,22 @@
         <v>19.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>256</v>
+        <v>56.8</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="W21" s="12" t="n">
+      <c r="W21" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2217,15 +2278,17 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D22" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="E22" s="9" t="n">
-        <v>1.7</v>
+      <c r="E22" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>10.8</v>
@@ -2243,13 +2306,13 @@
         <v>6.8</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="M22" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="M22" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>87</v>
@@ -2261,10 +2324,10 @@
         <v>23.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>68.3</v>
@@ -2272,20 +2335,20 @@
       <c r="U22" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W22" s="12" t="n">
+      <c r="W22" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>155.1</v>
+        <v>445.4</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>5.7</v>
+        <v>254.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2300,75 +2363,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="E23" s="10" t="n">
+      <c r="C23" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E23" s="9" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="F23" s="10" t="n">
-        <v>117.8</v>
+      <c r="F23" s="9" t="n">
+        <v>17.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>25.2</v>
+        <v>36.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>529.5</v>
+        <v>311.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="K23" s="10" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="K23" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="L23" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="M23" s="10" t="n">
-        <v>88</v>
+      <c r="L23" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>82</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>26.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q23" s="10" t="n">
-        <v>44</v>
-      </c>
-      <c r="R23" s="10" t="n">
-        <v>103.9</v>
+        <v>15.6</v>
+      </c>
+      <c r="Q23" s="9" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="R23" s="9" t="n">
+        <v>103.4</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>100.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>8267.799999999999</v>
+        <v>468</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="V23" s="10" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="W23" s="10" t="n">
-        <v>25.6</v>
+        <v>91.90000000000001</v>
+      </c>
+      <c r="V23" s="9" t="n">
+        <v>1123.5</v>
+      </c>
+      <c r="W23" s="9" t="n">
+        <v>935.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>94.8</v>
+        <v>26</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>205.4</v>
+        <v>7050.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>22.8</v>
+        <v>652.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2384,20 +2449,20 @@
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="9" t="n">
         <v>29.1</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="F24" s="10" t="n">
-        <v>37.5</v>
+      <c r="F24" s="9" t="n">
+        <v>23.5</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2405,53 +2470,51 @@
       <c r="J24" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L24" s="10" t="n">
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="M24" s="11" t="n">
         <v>17</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>18.4</v>
+        <v>0.1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q24" s="10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="R24" s="10" t="n">
+      <c r="Q24" s="9" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="R24" s="9" t="n">
         <v>20.7</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>53.5</v>
+        <v>0.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="V24" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W24" s="12" t="n">
-        <v>19.1</v>
+        <v>1.8</v>
+      </c>
+      <c r="V24" s="9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="W24" s="9" t="n">
+        <v>10.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>12.9</v>
+        <v>10</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>61</v>
+        <v>118.9</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>12.6</v>
+        <v>1.2</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2466,21 +2529,21 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>2.3</v>
+      <c r="C25" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E25" s="17" t="inlineStr"/>
+      <c r="F25" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>11.6</v>
+        <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10.6</v>
+        <v>1.2</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2492,40 +2555,48 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>10.8</v>
+        <v>7.6</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>16.9</v>
+        <v>16.3</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>83.5</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q25" s="14" t="inlineStr"/>
-      <c r="R25" s="12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q25" s="13" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="R25" s="11" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>662.3</v>
+        <v>405.5</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>12.8</v>
+        <v>156.1</v>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="W25" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X25" s="3" t="inlineStr"/>
-      <c r="Y25" s="3" t="inlineStr"/>
-      <c r="Z25" s="3" t="inlineStr"/>
+      <c r="W25" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2539,29 +2610,27 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>2.2</v>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="11" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>16</v>
+        <v>11.6</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>16.8</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.1</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
@@ -2572,42 +2641,44 @@
       <c r="M26" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R26" s="12" t="n">
+      <c r="R26" s="11" t="n">
         <v>21.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>12.2</v>
+        <v>52.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="V26" s="9" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="W26" s="12" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>18.6</v>
+        <v>28.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>19.8</v>
+        <v>112.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2622,74 +2693,76 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>12.7</v>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="11" t="n">
+        <v>27.4</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>7.2</v>
+        <v>15.2</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>12.8</v>
+        <v>22.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>16.8</v>
+        <v>11</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>68.7</v>
+        <v>6.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>18.1</v>
+        <v>10.6</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.4</v>
+        <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>22.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R27" s="12" t="n">
+      <c r="Q27" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R27" s="11" t="n">
         <v>20.8</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W27" s="12" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="V27" s="13" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="W27" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="Y27" s="3" t="inlineStr"/>
-      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="Y27" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2703,42 +2776,44 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="9" t="n">
-        <v>1.5</v>
+      <c r="C28" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>27.4</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>1.7</v>
+        <v>18.8</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>16</v>
+      <c r="H28" s="14" t="n">
+        <v>66</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>7.2</v>
+        <v>8.9</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L28" s="14" t="n">
         <v>18.4</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>11.6</v>
+        <v>16.6</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>10.7</v>
+        <v>17.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>3.4</v>
@@ -2746,29 +2821,33 @@
       <c r="Q28" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="R28" s="12" t="n">
+      <c r="R28" s="11" t="n">
         <v>20.8</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>56.7</v>
+        <v>56.9</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="W28" s="12" t="n">
-        <v>19.8</v>
+        <v>29.6</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y28" s="3" t="inlineStr"/>
-      <c r="Z28" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2782,12 +2861,14 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="n">
-        <v>6.8</v>
+      <c r="C29" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>26.8</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>17.4</v>
+        <v>15.9</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>22.1</v>
@@ -2795,17 +2876,17 @@
       <c r="G29" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="14" t="n">
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>18.6</v>
@@ -2825,26 +2906,26 @@
       <c r="Q29" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="R29" s="12" t="n">
+      <c r="R29" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>1.8</v>
+        <v>59.8</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>152.5</v>
+        <v>13.2</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="W29" s="12" t="n">
+      <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>19.8</v>
+      <c r="X29" s="14" t="n">
+        <v>19</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2865,52 +2946,50 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>1334.8</v>
-      </c>
-      <c r="E30" s="10" t="n">
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="11" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="E30" s="9" t="n">
         <v>85.8</v>
       </c>
-      <c r="F30" s="10" t="n">
-        <v>109.8</v>
+      <c r="F30" s="9" t="n">
+        <v>9.5</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>48.4</v>
+        <v>474.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="K30" s="10" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="L30" s="10" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="M30" s="10" t="n">
-        <v>185.4</v>
+        <v>39.8</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>308.4</v>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>9434.799999999999</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>83.40000000000001</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>904.6</v>
+        <v>90.2</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>43464.4</v>
+        <v>681.1</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="9" t="n">
         <v>132</v>
       </c>
-      <c r="R30" s="12" t="n">
+      <c r="R30" s="11" t="n">
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -2920,22 +2999,22 @@
         <v>298.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="V30" s="10" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="W30" s="10" t="n">
-        <v>99.59999999999999</v>
+        <v>10.8</v>
+      </c>
+      <c r="V30" s="9" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="W30" s="9" t="n">
+        <v>90.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>418.1</v>
+        <v>0.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>3136.2</v>
+        <v>916.2</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>4.6</v>
+        <v>47.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2951,22 +3030,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D31" s="11" t="n">
         <v>26.6</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="9" t="n">
         <v>21.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>26.1</v>
+        <v>1.6</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>4</v>
@@ -2974,29 +3053,27 @@
       <c r="J31" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="L31" s="10" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M31" s="10" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="9" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M31" s="9" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>18</v>
+        <v>10.1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>205.1</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="9" t="n">
         <v>26.4</v>
       </c>
-      <c r="R31" s="12" t="n">
-        <v>20.4</v>
+      <c r="R31" s="9" t="n">
+        <v>10.4</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>20.4</v>
@@ -3005,22 +3082,22 @@
         <v>59.8</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="V31" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V31" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="W31" s="12" t="n">
+      <c r="W31" s="9" t="n">
         <v>19.1</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>475.1</v>
+        <v>17.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>10</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3036,10 +3113,12 @@
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E32" s="14" t="inlineStr"/>
+      <c r="D32" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>13.6</v>
+      </c>
       <c r="F32" s="3" t="n">
         <v>21.9</v>
       </c>
@@ -3047,60 +3126,56 @@
         <v>8.6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>15.2</v>
+        <v>0.1</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="L32" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R32" s="12" t="n">
-        <v>19.8</v>
+        <v>4.8</v>
+      </c>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>7.4</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="V32" s="12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W32" s="12" t="n">
-        <v>18.8</v>
+        <v>96.8</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>198.1</v>
+      </c>
+      <c r="V32" s="11" t="inlineStr"/>
+      <c r="W32" s="13" t="n">
+        <v>44.91</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>19.8</v>
+        <v>4412.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>81.8</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>14.6</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3116,13 +3191,13 @@
       </c>
       <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>1.8</v>
+        <v>26.6</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>23.1</v>
+        <v>21.9</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>9.4</v>
@@ -3134,19 +3209,19 @@
         <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="L33" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="M33" s="9" t="n">
-        <v>1.5</v>
+      <c r="M33" s="14" t="n">
+        <v>19.6</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>84</v>
@@ -3155,24 +3230,24 @@
         <v>3.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="R33" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="R33" s="3" t="n">
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.5</v>
+        <v>19.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>56</v>
+        <v>256</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V33" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V33" s="11" t="n">
         <v>21.8</v>
       </c>
-      <c r="W33" s="12" t="n">
+      <c r="W33" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3181,7 +3256,9 @@
       <c r="Y33" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="Z33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="n">
+        <v>5.6</v>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3196,17 +3273,17 @@
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>1.7</v>
+      <c r="D34" s="13" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>1.8</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>20.9</v>
+        <v>23.1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>16.6</v>
+        <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>17</v>
@@ -3218,9 +3295,9 @@
         <v>7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L34" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L34" s="14" t="n">
         <v>18.4</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3230,7 +3307,7 @@
         <v>18.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2</v>
@@ -3238,7 +3315,7 @@
       <c r="Q34" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="R34" s="12" t="n">
+      <c r="R34" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3248,19 +3325,23 @@
         <v>57.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="V34" s="12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="V34" s="11" t="n">
         <v>24.6</v>
       </c>
-      <c r="W34" s="12" t="n">
+      <c r="W34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="Y34" s="3" t="inlineStr"/>
-      <c r="Z34" s="3" t="inlineStr"/>
+      <c r="Y34" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>10.8</v>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3274,20 +3355,18 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>3.2</v>
+        <v>24.2</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>28.9</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>10.8</v>
+        <v>6.6</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>16.8</v>
@@ -3301,47 +3380,51 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="12" t="n">
-        <v>17.6</v>
+      <c r="L35" s="14" t="n">
+        <v>17.9</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q35" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R35" s="12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="R35" s="3" t="n">
         <v>19</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>62.2</v>
+        <v>82.2</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V35" s="12" t="n">
+      <c r="V35" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="12" t="n">
+      <c r="W35" s="14" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="Y35" s="3" t="inlineStr"/>
-      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3357,13 +3440,13 @@
       </c>
       <c r="C36" s="3" t="inlineStr"/>
       <c r="D36" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>1.8</v>
+        <v>28.6</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>12.2</v>
+        <v>23.2</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>10.8</v>
@@ -3380,11 +3463,11 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="12" t="n">
-        <v>18.6</v>
+      <c r="L36" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>7.2</v>
+        <v>17.2</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>18.8</v>
@@ -3398,29 +3481,29 @@
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="12" t="n">
+      <c r="R36" s="14" t="n">
         <v>21.8</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>26.4</v>
+        <v>56.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="V36" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V36" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="W36" s="12" t="n">
+      <c r="W36" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>86.5</v>
+        <v>86.8</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3437,71 +3520,71 @@
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="10" t="n">
-        <v>1138.8</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>111</v>
+      <c r="D37" s="9" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>8821.799999999999</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>498.6</v>
+        <v>45.6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>898</v>
+        <v>87</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>210.9</v>
+        <v>40.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="K37" s="10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L37" s="12" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="L37" s="9" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="M37" s="10" t="n">
-        <v>82.59999999999999</v>
+      <c r="M37" s="9" t="n">
+        <v>4.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>82.2</v>
+        <v>0.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>12.6</v>
+        <v>20.8</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="Q37" s="10" t="n">
-        <v>132.8</v>
-      </c>
-      <c r="R37" s="12" t="n">
-        <v>102.2</v>
+        <v>149.4</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="R37" s="9" t="n">
+        <v>1082.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>10.1</v>
+        <v>1181.5</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>208.6</v>
+        <v>288.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="V37" s="12" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="V37" s="9" t="n">
         <v>109.8</v>
       </c>
-      <c r="W37" s="10" t="n">
-        <v>18.4</v>
+      <c r="W37" s="9" t="n">
+        <v>998.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>10.1</v>
+        <v>101.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>156</v>
+        <v>88</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3520,17 +3603,17 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>17</v>
@@ -3539,19 +3622,17 @@
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L38" s="12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="9" t="n">
         <v>16.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>17.9</v>
+        <v>1.8</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>86.09999999999999</v>
@@ -3559,34 +3640,36 @@
       <c r="P38" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="R38" s="12" t="n">
+      <c r="R38" s="9" t="n">
         <v>20.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>88.5</v>
+        <v>28.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>57.7</v>
+        <v>5.4</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V38" s="10" t="n">
-        <v>240.1</v>
-      </c>
-      <c r="W38" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>20.3</v>
+      <c r="V38" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="W38" s="9" t="n">
+        <v>12790.1</v>
+      </c>
+      <c r="X38" s="14" t="n">
+        <v>111.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3600,72 +3683,76 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>43.6</v>
+      <c r="C39" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>4.6</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
         <v>8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L39" s="12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L39" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>8.4</v>
+        <v>84.8</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R39" s="14" t="inlineStr"/>
-      <c r="S39" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q39" s="13" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="R39" s="13" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="S39" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="V39" s="12" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="W39" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="V39" s="13" t="n">
+        <v>75.42999999999999</v>
+      </c>
+      <c r="W39" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="X39" s="14" t="n">
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="Z39" s="3" t="inlineStr"/>
+        <v>64.8</v>
+      </c>
+      <c r="Z39" s="3" t="n">
+        <v>48.8</v>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3679,65 +3766,65 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C40" s="3" t="inlineStr"/>
       <c r="D40" s="3" t="n">
-        <v>16.2</v>
+        <v>26.2</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>22.8</v>
+        <v>22.2</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>8.4</v>
+        <v>16.4</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="L40" s="12" t="n">
+      <c r="J40" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L40" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="N40" s="8" t="n">
+      <c r="N40" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>84</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V40" s="12" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="U40" s="14" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="V40" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W40" s="3" t="n">
+      <c r="W40" s="11" t="n">
         <v>18.6</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3761,25 +3848,25 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.1</v>
+        <v>11.1</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>21.9</v>
+        <v>20.4</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>2.1</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>17</v>
+        <v>20.1</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>43.5</v>
+        <v>3.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
@@ -3787,49 +3874,49 @@
       <c r="K41" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="L41" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M41" s="9" t="n">
-        <v>1.7</v>
+      <c r="M41" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>18.3</v>
+        <v>1.8</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="P41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q41" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.5</v>
+        <v>62.9</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V41" s="12" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W41" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W41" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3844,36 +3931,38 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="n">
-        <v>30.4</v>
+      <c r="D42" s="13" t="n">
+        <v>48.6</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="F42" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>14</v>
+      <c r="F42" s="14" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>94</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr"/>
+        <v>65.40000000000001</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="12" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="M42" s="3" t="n">
+      <c r="L42" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M42" s="14" t="n">
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>17.8</v>
+        <v>17</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>85</v>
@@ -3884,30 +3973,32 @@
       <c r="Q42" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R42" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>20.4</v>
+      </c>
       <c r="T42" s="3" t="n">
         <v>52</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V42" s="12" t="n">
+      <c r="V42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="11" t="n">
         <v>20</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>57</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3924,17 +4015,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F43" s="14" t="inlineStr"/>
-      <c r="G43" s="8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>19.2</v>
+        <v>20.4</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>174.4</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>8.6</v>
@@ -3945,17 +4038,17 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="L43" s="14" t="n">
         <v>16.4</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="14" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>3</v>
@@ -3964,31 +4057,31 @@
         <v>20.4</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v>18.8</v>
+        <v>20.6</v>
+      </c>
+      <c r="S43" s="14" t="n">
+        <v>18</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="V43" s="12" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="V43" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W43" s="3" t="n">
+      <c r="W43" s="11" t="n">
         <v>20</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>57</v>
+        <v>14.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>14.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4004,51 +4097,51 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>98</v>
-      </c>
-      <c r="E44" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E44" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="F44" s="9" t="n">
-        <v>21.7</v>
+      <c r="F44" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>14.2</v>
+        <v>26.1</v>
       </c>
       <c r="H44" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
         <v>15.8</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>1.5</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="12" t="n">
+      <c r="L44" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>80.8</v>
+        <v>154.8</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="R44" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="R44" s="14" t="n">
         <v>21.8</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4057,12 +4150,14 @@
       <c r="T44" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="12" t="n">
+      <c r="U44" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W44" s="3" t="n">
-        <v>30</v>
+      <c r="W44" s="11" t="n">
+        <v>20.6</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4070,7 +4165,9 @@
       <c r="Y44" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="Z44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4085,71 +4182,75 @@
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>830.6</v>
+      <c r="D45" s="9" t="n">
+        <v>1165.8</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>135.9</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>22</v>
+        <v>53.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="K45" s="10" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="L45" s="10" t="n">
-        <v>1089.6</v>
-      </c>
-      <c r="M45" s="10" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="M45" s="9" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O45" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>499</v>
+      </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="Q45" s="10" t="n">
-        <v>650.2</v>
-      </c>
-      <c r="R45" s="10" t="n">
-        <v>1.3</v>
+      <c r="Q45" s="9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="R45" s="9" t="n">
+        <v>1191.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>746.4</v>
+        <v>115.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>217.9</v>
+        <v>517.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>107.1</v>
-      </c>
-      <c r="V45" s="10" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="W45" s="10" t="n">
-        <v>114.8</v>
+        <v>187.1</v>
+      </c>
+      <c r="V45" s="9" t="n">
+        <v>1543</v>
+      </c>
+      <c r="W45" s="9" t="n">
+        <v>111.5</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.8</v>
+        <v>392.9</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr"/>
+        <v>69.40000000000001</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>11141.1</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4164,17 +4265,17 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="10" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="E46" s="10" t="n">
+      <c r="D46" s="9" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E46" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>22.8</v>
+      <c r="F46" s="9" t="n">
+        <v>22.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.8</v>
+        <v>19.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4185,50 +4286,54 @@
       <c r="J46" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="12" t="n">
+      <c r="K46" s="3" t="n">
+        <v>72162.8</v>
+      </c>
+      <c r="L46" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="N46" s="3" t="n">
-        <v>17.2</v>
+      <c r="N46" s="14" t="n">
+        <v>54.9</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q46" s="10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="Q46" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="3" t="n">
-        <v>19.3</v>
+      <c r="S46" s="14" t="n">
+        <v>19.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="V46" s="12" t="n">
+      <c r="V46" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="11" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>19.1</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="Z46" s="3" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -35,20 +35,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,16 +140,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,16 +152,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,17 +769,17 @@
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="n">
-        <v>11.1</v>
+      <c r="D4" s="8" t="n">
+        <v>1.1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="10" t="n">
         <v>23</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>18.2</v>
@@ -808,25 +790,25 @@
       <c r="J4" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K4" s="11" t="n">
+      <c r="K4" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="L4" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M4" s="13" t="n">
-        <v>86.8</v>
+      <c r="L4" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>16.8</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>17</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q4" s="13" t="n">
+      <c r="Q4" s="8" t="n">
         <v>84</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -839,8 +821,8 @@
         <v>20.5</v>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr"/>
-      <c r="W4" s="11" t="inlineStr"/>
+      <c r="V4" s="10" t="inlineStr"/>
+      <c r="W4" s="10" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -858,7 +840,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>28.4</v>
@@ -866,7 +848,7 @@
       <c r="E5" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="10" t="n">
         <v>23</v>
       </c>
       <c r="G5" s="3" t="n">
@@ -881,20 +863,20 @@
       <c r="J5" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="M5" s="3" t="n">
+      <c r="L5" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M5" s="10" t="n">
         <v>15.8</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>3.4</v>
@@ -914,10 +896,10 @@
       <c r="U5" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V5" s="11" t="n">
+      <c r="V5" s="10" t="n">
         <v>24.8</v>
       </c>
-      <c r="W5" s="11" t="n">
+      <c r="W5" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -951,8 +933,8 @@
       <c r="E6" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>23.9</v>
+      <c r="F6" s="10" t="n">
+        <v>23.2</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>10.8</v>
@@ -966,20 +948,20 @@
       <c r="J6" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>3</v>
@@ -994,15 +976,15 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>58</v>
+        <v>58.3</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V6" s="11" t="n">
+      <c r="V6" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="W6" s="11" t="n">
+      <c r="W6" s="10" t="n">
         <v>20</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1028,7 +1010,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>30.4</v>
@@ -1036,7 +1018,7 @@
       <c r="E7" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="G7" s="3" t="n">
@@ -1046,18 +1028,18 @@
         <v>15.6</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="13" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="M7" s="14" t="n">
+      <c r="L7" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M7" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1069,8 +1051,8 @@
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="13" t="n">
-        <v>0.4</v>
+      <c r="Q7" s="3" t="n">
+        <v>30.4</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>20.6</v>
@@ -1079,22 +1061,22 @@
         <v>18.5</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>656.4</v>
+        <v>56.4</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="V7" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="W7" s="11" t="n">
+      <c r="W7" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="X7" s="14" t="n">
+      <c r="X7" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>27.8</v>
+        <v>57.8</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>14</v>
@@ -1119,14 +1101,14 @@
       <c r="E8" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="F8" s="11" t="n">
-        <v>23.59</v>
+      <c r="F8" s="10" t="n">
+        <v>23.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>19.4</v>
+        <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>6.9</v>
@@ -1134,14 +1116,14 @@
       <c r="J8" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>17.4</v>
+      <c r="L8" s="10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>16.4</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>17.4</v>
@@ -1167,17 +1149,17 @@
       <c r="U8" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="V8" s="11" t="n">
+      <c r="V8" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="W8" s="11" t="n">
+      <c r="W8" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>2.4</v>
+        <v>24.2</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>19.4</v>
@@ -1197,7 +1179,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="9" t="n">
-        <v>148.8</v>
+        <v>145.8</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>887.1</v>
@@ -1206,24 +1188,24 @@
         <v>17.2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>27.1</v>
+        <v>57.1</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="K9" s="11" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="10" t="n">
         <v>91.7</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="10" t="n">
         <v>83.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1236,31 +1218,31 @@
         <v>16</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>142.8</v>
+        <v>145.8</v>
       </c>
       <c r="R9" s="9" t="n">
-        <v>1196</v>
+        <v>106</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>182.6</v>
+        <v>122.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>9255.1</v>
+        <v>255.1</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>127.2</v>
+        <v>12.7</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>971.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>26.2</v>
+        <v>56.2</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>67</v>
@@ -1285,7 +1267,7 @@
       <c r="E10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="10" t="n">
         <v>23.4</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1298,15 +1280,15 @@
         <v>6.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.1</v>
+        <v>11.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L10" s="9" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="M10" s="10" t="n">
         <v>16.6</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1325,25 +1307,25 @@
         <v>21.2</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>90.5</v>
+        <v>20.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V10" s="11" t="n">
+      <c r="V10" s="10" t="n">
         <v>25.4</v>
       </c>
-      <c r="W10" s="11" t="n">
+      <c r="W10" s="10" t="n">
         <v>19.5</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>13.4</v>
@@ -1362,13 +1344,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="8" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1378,7 +1360,7 @@
         <v>1.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1386,11 +1368,11 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="L11" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="M11" s="14" t="n">
-        <v>18.2</v>
+      <c r="M11" s="10" t="n">
+        <v>17.2</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>18.9</v>
@@ -1401,10 +1383,10 @@
       <c r="P11" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="11" t="n">
+      <c r="R11" s="10" t="n">
         <v>20</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1414,19 +1396,19 @@
         <v>425.4</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="13" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V11" s="8" t="n">
         <v>45.4</v>
       </c>
-      <c r="W11" s="13" t="n">
+      <c r="W11" s="8" t="n">
         <v>19.51</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>48.9</v>
+        <v>58.9</v>
       </c>
       <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1445,14 +1427,14 @@
       <c r="C12" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="10" t="n">
         <v>28.2</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="n">
-        <v>43.1</v>
+      <c r="F12" s="10" t="n">
+        <v>23.1</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>10.2</v>
@@ -1469,37 +1451,37 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="L12" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="M12" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>1.9</v>
+        <v>19.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>89</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Q12" s="13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R12" s="11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q12" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R12" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>257.1</v>
+        <v>57.1</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V12" s="13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V12" s="8" t="n">
         <v>45.4</v>
       </c>
       <c r="W12" s="3" t="n">
@@ -1528,13 +1510,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="10" t="n">
         <v>26</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F13" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F13" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1552,10 +1534,10 @@
       <c r="K13" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="11" t="n">
+      <c r="L13" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="10" t="n">
         <v>15.8</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1565,12 +1547,12 @@
         <v>83.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q13" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="R13" s="11" t="n">
+      <c r="R13" s="10" t="n">
         <v>19.9</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1611,14 +1593,14 @@
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="10" t="n">
         <v>27.4</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>23.8</v>
+      <c r="F14" s="10" t="n">
+        <v>23.3</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1629,34 +1611,34 @@
       <c r="I14" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="3" t="n">
         <v>11</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="11" t="n">
+      <c r="L14" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="14" t="n">
+      <c r="M14" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="N14" s="14" t="n">
+      <c r="N14" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>714.5</v>
+        <v>74.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="10" t="n">
         <v>26.8</v>
       </c>
-      <c r="R14" s="11" t="n">
+      <c r="R14" s="10" t="n">
         <v>19.4</v>
       </c>
-      <c r="S14" s="14" t="n">
+      <c r="S14" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="T14" s="3" t="n">
@@ -1694,13 +1676,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="10" t="n">
         <v>28.8</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="G15" s="3" t="n">
@@ -1718,10 +1700,10 @@
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="L15" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1733,10 +1715,10 @@
       <c r="P15" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="10" t="n">
         <v>28.8</v>
       </c>
-      <c r="R15" s="11" t="n">
+      <c r="R15" s="10" t="n">
         <v>21.2</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1779,7 +1761,7 @@
       <c r="C16" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="10" t="n">
         <v>138.8</v>
       </c>
       <c r="E16" s="9" t="n">
@@ -1792,7 +1774,7 @@
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>288.2</v>
+        <v>81.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.6</v>
@@ -1803,29 +1785,29 @@
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="9" t="n">
-        <v>92</v>
-      </c>
-      <c r="M16" s="9" t="n">
+      <c r="L16" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="M16" s="10" t="n">
         <v>84</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>909.4</v>
+        <v>904.4</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>40</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="Q16" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="Q16" s="10" t="n">
         <v>138.2</v>
       </c>
-      <c r="R16" s="11" t="n">
+      <c r="R16" s="10" t="n">
         <v>102.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>98.8</v>
+        <v>988.2</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>66.8</v>
@@ -1843,10 +1825,10 @@
         <v>95.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1862,16 +1844,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="10" t="n">
         <v>27.8</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>22.8</v>
       </c>
-      <c r="G17" s="14" t="n">
+      <c r="G17" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1884,50 +1866,50 @@
         <v>10.1</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="11" t="n">
+      <c r="L17" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="N17" s="14" t="n">
-        <v>19.1</v>
+      <c r="N17" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q17" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R17" s="9" t="n">
-        <v>11.4</v>
+      <c r="Q17" s="10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="R17" s="10" t="n">
+        <v>20.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>51.2</v>
+        <v>53.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>1.7</v>
+        <v>17.2</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1068.5</v>
+        <v>22.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>810.8</v>
+        <v>254.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1945,13 +1927,13 @@
       <c r="C18" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="10" t="n">
         <v>30.4</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="8" t="n">
         <v>44.5</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="8" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1966,13 +1948,13 @@
       <c r="J18" s="3" t="n">
         <v>126.1</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="13" t="n">
+      <c r="L18" s="8" t="n">
         <v>49.6</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="10" t="n">
         <v>16.2</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1984,10 +1966,10 @@
       <c r="P18" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q18" s="13" t="n">
+      <c r="Q18" s="8" t="n">
         <v>90.47</v>
       </c>
-      <c r="R18" s="13" t="n">
+      <c r="R18" s="8" t="n">
         <v>44.8</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1999,20 +1981,20 @@
       <c r="U18" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="V18" s="13" t="n">
+      <c r="V18" s="8" t="n">
         <v>46.47</v>
       </c>
-      <c r="W18" s="13" t="n">
+      <c r="W18" s="8" t="n">
         <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>86</v>
+        <v>14.4</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0.7</v>
+        <v>20.1</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2028,14 +2010,14 @@
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="10" t="n">
         <v>29.6</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>11.8</v>
@@ -2049,26 +2031,26 @@
       <c r="J19" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M19" s="11" t="n">
+      <c r="M19" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="N19" s="14" t="n">
-        <v>18.1</v>
+      <c r="N19" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="13" t="n">
-        <v>92.59999999999999</v>
+      <c r="Q19" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>20.8</v>
@@ -2083,7 +2065,7 @@
         <v>22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>19.8</v>
@@ -2092,7 +2074,7 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>294</v>
+        <v>54</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16</v>
@@ -2113,8 +2095,8 @@
       <c r="C20" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>10.6</v>
+      <c r="D20" s="10" t="n">
+        <v>30.6</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>18.2</v>
@@ -2122,11 +2104,11 @@
       <c r="F20" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="G20" s="14" t="n">
+      <c r="G20" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="H20" s="14" t="n">
-        <v>87.40000000000001</v>
+      <c r="H20" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>7.9</v>
@@ -2134,20 +2116,20 @@
       <c r="J20" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>0.8</v>
+      <c r="K20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M20" s="11" t="n">
+      <c r="M20" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>19</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>2.8</v>
@@ -2180,7 +2162,7 @@
         <v>58</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2196,14 +2178,14 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="10" t="n">
         <v>26.6</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="13" t="n">
-        <v>2.2</v>
+      <c r="F21" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>8.6</v>
@@ -2217,26 +2199,26 @@
       <c r="J21" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>0.8</v>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M21" s="11" t="n">
+      <c r="M21" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>20</v>
@@ -2245,10 +2227,10 @@
         <v>19.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>56.8</v>
+        <v>56</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>24.4</v>
@@ -2260,7 +2242,7 @@
         <v>18</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>12.6</v>
@@ -2279,9 +2261,9 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D22" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>28.4</v>
       </c>
       <c r="E22" s="3" t="n">
@@ -2302,17 +2284,17 @@
       <c r="J22" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="10" t="n">
         <v>6.8</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M22" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M22" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>87</v>
@@ -2324,7 +2306,7 @@
         <v>23.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>19.5</v>
@@ -2345,10 +2327,10 @@
         <v>445.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>254.9</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2366,17 +2348,17 @@
       <c r="C23" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>14.5</v>
+      <c r="D23" s="10" t="n">
+        <v>145.6</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>36.2</v>
+        <v>56.2</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>84.8</v>
@@ -2387,14 +2369,14 @@
       <c r="J23" s="3" t="n">
         <v>52.9</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="10" t="n">
         <v>6.8</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>92</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>82</v>
+        <v>93</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>85</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>92</v>
@@ -2418,13 +2400,13 @@
         <v>468</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>1123.5</v>
+        <v>123.5</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>935.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>26</v>
@@ -2433,7 +2415,7 @@
         <v>7050.1</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>652.8</v>
+        <v>62.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2449,7 +2431,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="10" t="n">
         <v>29.1</v>
       </c>
       <c r="E24" s="9" t="n">
@@ -2462,7 +2444,7 @@
         <v>11.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>6.6</v>
@@ -2474,20 +2456,20 @@
       <c r="L24" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="M24" s="11" t="n">
+      <c r="M24" s="10" t="n">
         <v>17</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>5.4</v>
+        <v>25.4</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>84.09999999999999</v>
+        <v>28.1</v>
       </c>
       <c r="R24" s="9" t="n">
         <v>20.7</v>
@@ -2496,25 +2478,25 @@
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1.8</v>
+        <v>18.3</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="W24" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X24" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="Y24" s="3" t="n">
-        <v>118.9</v>
+        <v>18.4</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>1.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2532,18 +2514,18 @@
       <c r="C25" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="10" t="n">
         <v>22.8</v>
       </c>
-      <c r="E25" s="17" t="inlineStr"/>
-      <c r="F25" s="3" t="n">
-        <v>19.4</v>
+      <c r="E25" s="13" t="inlineStr"/>
+      <c r="F25" s="10" t="n">
+        <v>19.2</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1.2</v>
+        <v>12</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2555,10 +2537,10 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>11.8</v>
+        <v>17.6</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>16.3</v>
@@ -2569,10 +2551,10 @@
       <c r="P25" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="Q25" s="13" t="n">
+      <c r="Q25" s="8" t="n">
         <v>91.40000000000001</v>
       </c>
-      <c r="R25" s="11" t="n">
+      <c r="R25" s="10" t="n">
         <v>19.4</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2582,7 +2564,7 @@
         <v>156.1</v>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="W25" s="3" t="n">
@@ -2592,7 +2574,7 @@
         <v>9.5</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>88.8</v>
+        <v>88</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>2.8</v>
@@ -2611,26 +2593,26 @@
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="10" t="n">
         <v>28.8</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>23.9</v>
+      <c r="F26" s="10" t="n">
+        <v>23</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H26" s="14" t="n">
-        <v>16.8</v>
+      <c r="H26" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>8</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>30.4</v>
@@ -2638,22 +2620,22 @@
       <c r="L26" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R26" s="11" t="n">
+      <c r="R26" s="10" t="n">
         <v>21.2</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2665,7 +2647,7 @@
       <c r="U26" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2675,10 +2657,10 @@
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>28.8</v>
+        <v>58.5</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>112.8</v>
+        <v>12.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2693,21 +2675,23 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="11" t="n">
+      <c r="C27" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D27" s="10" t="n">
         <v>27.4</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F27" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F27" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11</v>
+        <v>16.2</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4</v>
@@ -2716,40 +2700,40 @@
         <v>6.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>11.8</v>
+        <v>18.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="R27" s="11" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="R27" s="10" t="n">
         <v>20.8</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="V27" s="13" t="n">
-        <v>64.8</v>
+      <c r="V27" s="10" t="n">
+        <v>24.8</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>19.8</v>
@@ -2779,34 +2763,34 @@
       <c r="C28" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="10" t="n">
         <v>27.4</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>22.8</v>
+        <v>18</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>22.7</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H28" s="14" t="n">
-        <v>66</v>
+      <c r="H28" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>8.9</v>
+        <v>2.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="L28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="10" t="n">
         <v>16.6</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2821,32 +2805,32 @@
       <c r="Q28" s="3" t="n">
         <v>27.4</v>
       </c>
-      <c r="R28" s="11" t="n">
+      <c r="R28" s="10" t="n">
         <v>20.8</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>56.9</v>
+        <v>56.7</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="V28" s="3" t="n">
-        <v>29.6</v>
+      <c r="V28" s="10" t="n">
+        <v>25.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>17.8</v>
+        <v>19.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>59.9</v>
+        <v>59.2</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2864,34 +2848,34 @@
       <c r="C29" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="10" t="n">
         <v>26.8</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F29" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F29" s="10" t="n">
         <v>22.1</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="H29" s="14" t="n">
+      <c r="H29" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2906,26 +2890,26 @@
       <c r="Q29" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="R29" s="11" t="n">
+      <c r="R29" s="10" t="n">
         <v>19.8</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>59.8</v>
+        <v>59.5</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="10" t="n">
         <v>23.6</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="X29" s="14" t="n">
-        <v>19</v>
+      <c r="X29" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>66.2</v>
@@ -2947,7 +2931,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="10" t="n">
         <v>133.2</v>
       </c>
       <c r="E30" s="9" t="n">
@@ -2960,13 +2944,13 @@
         <v>474.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>39.8</v>
+        <v>33</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>308.4</v>
@@ -2974,7 +2958,7 @@
       <c r="L30" s="9" t="n">
         <v>9434.799999999999</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="10" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2989,7 +2973,7 @@
       <c r="Q30" s="9" t="n">
         <v>132</v>
       </c>
-      <c r="R30" s="11" t="n">
+      <c r="R30" s="10" t="n">
         <v>102</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -2999,19 +2983,19 @@
         <v>298.9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>10.8</v>
+        <v>70.8</v>
       </c>
       <c r="V30" s="9" t="n">
         <v>71.59999999999999</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>90.59999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>916.2</v>
+        <v>336.2</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>47.6</v>
@@ -3032,20 +3016,20 @@
       <c r="C31" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="10" t="n">
         <v>26.6</v>
       </c>
       <c r="E31" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="10" t="n">
         <v>21.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1.6</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>4</v>
@@ -3055,16 +3039,16 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="9" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M31" s="9" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="M31" s="10" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>205.1</v>
+        <v>5.1</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>3</v>
@@ -3072,8 +3056,8 @@
       <c r="Q31" s="9" t="n">
         <v>26.4</v>
       </c>
-      <c r="R31" s="9" t="n">
-        <v>10.4</v>
+      <c r="R31" s="10" t="n">
+        <v>20.4</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>20.4</v>
@@ -3084,7 +3068,7 @@
       <c r="U31" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="10" t="n">
         <v>23.6</v>
       </c>
       <c r="W31" s="9" t="n">
@@ -3097,7 +3081,7 @@
         <v>17.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3113,13 +3097,13 @@
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="10" t="n">
         <v>26.2</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="10" t="n">
         <v>21.9</v>
       </c>
       <c r="G32" s="3" t="n">
@@ -3134,44 +3118,44 @@
       <c r="J32" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="K32" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" s="3" t="n">
+      <c r="K32" s="10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L32" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>4.8</v>
+        <v>29.8</v>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="13" t="n">
+      <c r="Q32" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>1.9</v>
+        <v>19.3</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>96.8</v>
+        <v>56.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>198.1</v>
       </c>
-      <c r="V32" s="11" t="inlineStr"/>
-      <c r="W32" s="13" t="n">
+      <c r="V32" s="10" t="inlineStr"/>
+      <c r="W32" s="8" t="n">
         <v>44.91</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>4412.8</v>
+        <v>912.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>81.8</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>14.6</v>
@@ -3190,13 +3174,13 @@
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="10" t="n">
         <v>26.6</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="10" t="n">
         <v>21.9</v>
       </c>
       <c r="G33" s="3" t="n">
@@ -3209,16 +3193,16 @@
         <v>3.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="K33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10" t="n">
         <v>17.4</v>
       </c>
-      <c r="M33" s="14" t="n">
-        <v>19.6</v>
+      <c r="M33" s="10" t="n">
+        <v>15.6</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>16.7</v>
@@ -3236,15 +3220,15 @@
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>256</v>
+        <v>56</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V33" s="11" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="V33" s="10" t="n">
         <v>21.8</v>
       </c>
       <c r="W33" s="3" t="n">
@@ -3257,7 +3241,7 @@
         <v>75</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3273,13 +3257,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="13" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="E34" s="13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F34" s="3" t="n">
+      <c r="D34" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F34" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="G34" s="3" t="n">
@@ -3294,13 +3278,13 @@
       <c r="J34" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K34" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L34" s="14" t="n">
+      <c r="K34" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="10" t="n">
         <v>17.2</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3325,9 +3309,9 @@
         <v>57.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="V34" s="11" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="V34" s="10" t="n">
         <v>24.6</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3340,7 +3324,7 @@
         <v>67</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3356,14 +3340,14 @@
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="E35" s="13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>28.9</v>
+      <c r="E35" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>20.9</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>6.6</v>
@@ -3372,25 +3356,25 @@
         <v>16.8</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="14" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="M35" s="3" t="n">
+      <c r="L35" s="10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M35" s="10" t="n">
         <v>15.8</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>3.4</v>
@@ -3405,15 +3389,15 @@
         <v>18.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>82.2</v>
+        <v>62.2</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V35" s="11" t="n">
+      <c r="V35" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="W35" s="14" t="n">
+      <c r="W35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3423,7 +3407,7 @@
         <v>86.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3439,13 +3423,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="10" t="n">
         <v>28.6</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="10" t="n">
         <v>23.2</v>
       </c>
       <c r="G36" s="3" t="n">
@@ -3460,13 +3444,13 @@
       <c r="J36" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="M36" s="3" t="n">
+      <c r="L36" s="10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M36" s="10" t="n">
         <v>17.2</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3481,7 +3465,7 @@
       <c r="Q36" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R36" s="14" t="n">
+      <c r="R36" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3491,9 +3475,9 @@
         <v>56.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V36" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="V36" s="10" t="n">
         <v>20.4</v>
       </c>
       <c r="W36" s="3" t="n">
@@ -3503,7 +3487,7 @@
         <v>20.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3519,12 +3503,14 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D37" s="9" t="n">
-        <v>120.8</v>
+        <v>132.8</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>8821.799999999999</v>
+        <v>882.1</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>11</v>
@@ -3541,10 +3527,10 @@
       <c r="J37" s="3" t="n">
         <v>31.5</v>
       </c>
-      <c r="K37" s="9" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="L37" s="9" t="n">
+      <c r="K37" s="10" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="L37" s="10" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="M37" s="9" t="n">
@@ -3554,19 +3540,19 @@
         <v>0.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>20.8</v>
+        <v>30.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>149.4</v>
+        <v>14.4</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>131.8</v>
+        <v>133.8</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>1082.2</v>
+        <v>162.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1181.5</v>
+        <v>101.7</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>288.6</v>
@@ -3578,13 +3564,13 @@
         <v>109.8</v>
       </c>
       <c r="W37" s="9" t="n">
-        <v>998.1</v>
+        <v>250.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>101.4</v>
+        <v>14.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>31.2</v>
@@ -3603,36 +3589,36 @@
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="10" t="n">
         <v>26.8</v>
       </c>
       <c r="E38" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="10" t="n">
         <v>22.2</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>17</v>
+        <v>1.7</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="9" t="n">
+      <c r="L38" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="10" t="n">
         <v>16.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.8</v>
+        <v>17.9</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>86.09999999999999</v>
@@ -3650,25 +3636,25 @@
         <v>28.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>5.4</v>
+        <v>0.1</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="V38" s="11" t="n">
+      <c r="V38" s="10" t="n">
         <v>22</v>
       </c>
       <c r="W38" s="9" t="n">
-        <v>12790.1</v>
-      </c>
-      <c r="X38" s="14" t="n">
-        <v>111.9</v>
+        <v>11.1</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>1.4</v>
+        <v>11.1</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3684,15 +3670,15 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D39" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D39" s="8" t="n">
         <v>46.3</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="G39" s="3" t="n">
@@ -3705,50 +3691,50 @@
       <c r="J39" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K39" s="3" t="n">
-        <v>9.6</v>
+      <c r="K39" s="10" t="n">
+        <v>3.6</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="10" t="n">
         <v>17.6</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>19</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>84.8</v>
+        <v>84</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q39" s="13" t="n">
+      <c r="Q39" s="10" t="n">
         <v>46.65</v>
       </c>
-      <c r="R39" s="13" t="n">
+      <c r="R39" s="10" t="n">
         <v>20.48</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="V39" s="13" t="n">
+      <c r="V39" s="8" t="n">
         <v>75.42999999999999</v>
       </c>
-      <c r="W39" s="11" t="n">
+      <c r="W39" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="X39" s="14" t="n">
+      <c r="X39" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>64.8</v>
+        <v>64.5</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>48.8</v>
@@ -3770,14 +3756,14 @@
       <c r="D40" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="E40" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F40" s="3" t="n">
+      <c r="E40" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F40" s="10" t="n">
         <v>22.2</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.8</v>
+        <v>7.8</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>16.4</v>
@@ -3786,15 +3772,15 @@
         <v>2.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>22.1</v>
+        <v>5.4</v>
+      </c>
+      <c r="K40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="10" t="n">
         <v>17.4</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -3806,11 +3792,11 @@
       <c r="P40" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q40" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>20.8</v>
+      <c r="Q40" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R40" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>19.7</v>
@@ -3818,13 +3804,13 @@
       <c r="T40" s="3" t="n">
         <v>57.8</v>
       </c>
-      <c r="U40" s="14" t="n">
-        <v>94.40000000000001</v>
+      <c r="U40" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W40" s="11" t="n">
+      <c r="W40" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3848,16 +3834,16 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E41" s="13" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>2.1</v>
+        <v>25.4</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>21.9</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>20.1</v>
@@ -3871,50 +3857,50 @@
       <c r="J41" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="10" t="n">
         <v>5.8</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>15.2</v>
+      <c r="M41" s="10" t="n">
+        <v>17.2</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>1.8</v>
+        <v>18.3</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>81</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q41" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q41" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="R41" s="3" t="n">
-        <v>17.8</v>
+      <c r="R41" s="10" t="n">
+        <v>17.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.9</v>
+        <v>62.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="V41" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="W41" s="11" t="n">
+      <c r="V41" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W41" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76</v>
+        <v>76.5</v>
       </c>
       <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
@@ -3931,34 +3917,34 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="13" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="E42" s="3" t="n">
+      <c r="D42" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E42" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="F42" s="14" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="G42" s="14" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H42" s="14" t="n">
-        <v>94</v>
+      <c r="F42" s="10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M42" s="14" t="n">
+      <c r="M42" s="10" t="n">
         <v>15.8</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -3970,10 +3956,10 @@
       <c r="P42" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="10" t="n">
         <v>21</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -3988,17 +3974,17 @@
       <c r="V42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W42" s="11" t="n">
+      <c r="W42" s="10" t="n">
         <v>20</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>1.4</v>
+        <v>14.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>1.4</v>
+        <v>57</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4015,19 +4001,19 @@
       </c>
       <c r="C43" s="3" t="inlineStr"/>
       <c r="D43" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E43" s="13" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>12.1</v>
+        <v>30.4</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>22.7</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H43" s="14" t="n">
-        <v>174.4</v>
+        <v>15.4</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>8.6</v>
@@ -4035,43 +4021,43 @@
       <c r="J43" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="14" t="n">
+      <c r="L43" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M43" s="14" t="n">
+      <c r="M43" s="10" t="n">
         <v>14.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>13.9</v>
+        <v>15.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q43" s="3" t="n">
+      <c r="Q43" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="S43" s="14" t="n">
-        <v>18</v>
+      <c r="S43" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>25.9</v>
+        <v>25</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W43" s="11" t="n">
+      <c r="W43" s="10" t="n">
         <v>20</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4081,7 +4067,7 @@
         <v>14.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>21.9</v>
+        <v>57</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4102,46 +4088,46 @@
       <c r="D44" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="F44" s="14" t="n">
-        <v>12</v>
+      <c r="F44" s="10" t="n">
+        <v>22</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>26.1</v>
+        <v>14.2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="K44" s="3" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K44" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M44" s="3" t="n">
-        <v>12.6</v>
+      <c r="M44" s="10" t="n">
+        <v>15.6</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>154.8</v>
+        <v>82</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="R44" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="R44" s="10" t="n">
         <v>21.8</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4151,13 +4137,13 @@
         <v>47</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>2.3</v>
+        <v>23.2</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W44" s="11" t="n">
-        <v>20.6</v>
+      <c r="W44" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>19.6</v>
@@ -4166,7 +4152,7 @@
         <v>14.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>21</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4181,15 +4167,17 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D45" s="9" t="n">
-        <v>1165.8</v>
-      </c>
-      <c r="E45" s="9" t="n">
+        <v>167.8</v>
+      </c>
+      <c r="E45" s="10" t="n">
         <v>102.8</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>135.9</v>
+        <v>135.3</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>65</v>
@@ -4198,25 +4186,25 @@
         <v>92.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>53.5</v>
+        <v>33.5</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>61.3</v>
       </c>
-      <c r="K45" s="9" t="n">
-        <v>59.4</v>
+      <c r="K45" s="10" t="n">
+        <v>9.4</v>
       </c>
       <c r="L45" s="9" t="n">
         <v>109.6</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" s="10" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>499</v>
+        <v>99</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
@@ -4225,31 +4213,31 @@
         <v>16.5</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>1191.1</v>
+        <v>121</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>115.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>517.9</v>
+        <v>17.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>187.1</v>
+        <v>107.1</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>1543</v>
+        <v>143</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>111.5</v>
+        <v>115</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>392.9</v>
+        <v>93.5</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>11141.1</v>
+        <v>114</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4268,14 +4256,14 @@
       <c r="D46" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="10" t="n">
         <v>17.1</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="10" t="n">
         <v>22.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>19.8</v>
+        <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>15.4</v>
@@ -4287,31 +4275,31 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>72162.8</v>
+        <v>51.8</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="N46" s="14" t="n">
-        <v>54.9</v>
+      <c r="N46" s="3" t="n">
+        <v>51.1</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="Q46" s="9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q46" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="S46" s="14" t="n">
-        <v>19.8</v>
+      <c r="S46" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>53</v>
@@ -4322,7 +4310,7 @@
       <c r="V46" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="W46" s="11" t="n">
+      <c r="W46" s="10" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">
@@ -4332,7 +4320,7 @@
         <v>3.6</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="8" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>27.8</v>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>28.6</v>
@@ -976,7 +976,7 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>58.3</v>
+        <v>56.3</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
@@ -1046,7 +1046,7 @@
         <v>19.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
@@ -1111,7 +1111,7 @@
         <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
@@ -1129,7 +1129,7 @@
         <v>17.4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>4</v>
@@ -1233,7 +1233,7 @@
         <v>99.59999999999999</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>12.7</v>
+        <v>127.2</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>97.40000000000001</v>
@@ -1285,8 +1285,8 @@
       <c r="K10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="10" t="n">
-        <v>18.3</v>
+      <c r="L10" s="9" t="n">
+        <v>18.6</v>
       </c>
       <c r="M10" s="10" t="n">
         <v>16.6</v>
@@ -1325,7 +1325,7 @@
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>13.4</v>
@@ -1365,7 +1365,7 @@
       <c r="J11" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="10" t="n">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>28.2</v>
@@ -1448,7 +1448,7 @@
       <c r="J12" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="10" t="n">
@@ -1531,8 +1531,8 @@
       <c r="J13" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="K13" s="3" t="n">
-        <v>8</v>
+      <c r="K13" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="L13" s="10" t="n">
         <v>17.6</v>
@@ -1614,7 +1614,7 @@
       <c r="J14" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="10" t="n">
@@ -1683,7 +1683,7 @@
         <v>17.8</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11</v>
@@ -1697,7 +1697,7 @@
       <c r="J15" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="10" t="n">
@@ -1774,7 +1774,7 @@
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.2</v>
+        <v>84.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.6</v>
@@ -1782,7 +1782,7 @@
       <c r="J16" s="3" t="n">
         <v>50.6</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="10" t="n">
@@ -1825,7 +1825,7 @@
         <v>95.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>2</v>
+        <v>302</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>61</v>
@@ -1903,13 +1903,13 @@
         <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>15.7</v>
+        <v>19.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>22.2</v>
+        <v>120.1</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>254.1</v>
+        <v>902.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>30.4</v>
@@ -1988,10 +1988,10 @@
         <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>20.1</v>
+        <v>0.1</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>58</v>
@@ -2017,7 +2017,7 @@
         <v>17.8</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>11.8</v>
@@ -2074,7 +2074,7 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>54</v>
+        <v>28.2</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16</v>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>30.6</v>
@@ -2218,7 +2218,7 @@
         <v>2.8</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>20</v>
@@ -2330,7 +2330,7 @@
         <v>76</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D23" s="10" t="n">
         <v>145.6</v>
@@ -2355,7 +2355,7 @@
         <v>89.40000000000001</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>56.2</v>
@@ -2478,19 +2478,19 @@
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>2.2</v>
+        <v>13.6</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>11.7</v>
+        <v>24.7</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>18.4</v>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D25" s="10" t="n">
         <v>22.8</v>
@@ -2525,7 +2525,7 @@
         <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12</v>
+        <v>19.6</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2606,7 +2606,7 @@
         <v>11.6</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.6</v>
@@ -2685,7 +2685,7 @@
         <v>17.2</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>10.2</v>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>27.4</v>
@@ -2776,13 +2776,13 @@
         <v>9.4</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -2944,7 +2944,7 @@
         <v>474.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
@@ -2989,7 +2989,7 @@
         <v>71.59999999999999</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>9.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>0.7</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D31" s="10" t="n">
         <v>26.6</v>
@@ -3039,16 +3039,16 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="9" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="M31" s="10" t="n">
         <v>16.7</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>5.1</v>
+        <v>25.6</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>3</v>
@@ -3063,10 +3063,10 @@
         <v>20.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>59.8</v>
+        <v>59.2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.4</v>
+        <v>14.2</v>
       </c>
       <c r="V31" s="10" t="n">
         <v>23.6</v>
@@ -3078,7 +3078,7 @@
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>18</v>
@@ -3116,7 +3116,7 @@
         <v>4.6</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="K32" s="10" t="n">
         <v>7.2</v>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="8" t="n">
@@ -3152,10 +3152,10 @@
         <v>44.91</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>912.2</v>
+        <v>9119.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>1.5</v>
+        <v>26.2</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>14.6</v>
@@ -3220,7 +3220,7 @@
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>56</v>
@@ -3339,7 +3339,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D35" s="10" t="n">
         <v>24.2</v>
       </c>
@@ -3356,7 +3358,7 @@
         <v>16.8</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>5.2</v>
@@ -3504,7 +3506,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>132.8</v>
@@ -3549,10 +3551,10 @@
         <v>133.8</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>162.2</v>
+        <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>101.7</v>
+        <v>218.8</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>288.6</v>
@@ -3564,10 +3566,10 @@
         <v>109.8</v>
       </c>
       <c r="W37" s="9" t="n">
-        <v>250.1</v>
+        <v>95</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>14.3</v>
+        <v>1014.3</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>86</v>
@@ -3602,7 +3604,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>1.7</v>
+        <v>17</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.2</v>
@@ -3624,7 +3626,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.9</v>
+        <v>29.9</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>26.8</v>
@@ -3648,13 +3650,13 @@
         <v>11.1</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="Y38" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>88.8</v>
+        <v>21.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3678,7 +3680,7 @@
       <c r="E39" s="10" t="n">
         <v>18.6</v>
       </c>
-      <c r="F39" s="10" t="n">
+      <c r="F39" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="G39" s="3" t="n">
@@ -3694,7 +3696,7 @@
       <c r="K39" s="10" t="n">
         <v>3.6</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="10" t="n">
         <v>19.4</v>
       </c>
       <c r="M39" s="10" t="n">
@@ -3709,7 +3711,7 @@
       <c r="P39" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q39" s="10" t="n">
+      <c r="Q39" s="8" t="n">
         <v>46.65</v>
       </c>
       <c r="R39" s="10" t="n">
@@ -3759,7 +3761,7 @@
       <c r="E40" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="F40" s="10" t="n">
+      <c r="F40" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3777,7 +3779,7 @@
       <c r="K40" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="10" t="n">
         <v>19.2</v>
       </c>
       <c r="M40" s="10" t="n">
@@ -3792,7 +3794,7 @@
       <c r="P40" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q40" s="10" t="n">
+      <c r="Q40" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="R40" s="10" t="n">
@@ -3834,7 +3836,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>25.4</v>
@@ -3842,7 +3844,7 @@
       <c r="E41" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="F41" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3852,7 +3854,7 @@
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
@@ -3860,7 +3862,7 @@
       <c r="K41" s="10" t="n">
         <v>5.8</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="10" t="n">
         <v>19.4</v>
       </c>
       <c r="M41" s="10" t="n">
@@ -3875,7 +3877,7 @@
       <c r="P41" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q41" s="10" t="n">
+      <c r="Q41" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R41" s="10" t="n">
@@ -3885,13 +3887,13 @@
         <v>17.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.5</v>
+        <v>62.2</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="V41" s="8" t="n">
-        <v>1.9</v>
+      <c r="V41" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="W41" s="10" t="n">
         <v>16.8</v>
@@ -3900,7 +3902,7 @@
         <v>17.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
@@ -3923,8 +3925,8 @@
       <c r="E42" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="F42" s="10" t="n">
-        <v>22.5</v>
+      <c r="F42" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>12.6</v>
@@ -3941,8 +3943,8 @@
       <c r="K42" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>18.4</v>
+      <c r="L42" s="10" t="n">
+        <v>17.4</v>
       </c>
       <c r="M42" s="10" t="n">
         <v>15.8</v>
@@ -3956,7 +3958,7 @@
       <c r="P42" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q42" s="10" t="n">
+      <c r="Q42" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R42" s="10" t="n">
@@ -4006,8 +4008,8 @@
       <c r="E43" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="F43" s="10" t="n">
-        <v>22.7</v>
+      <c r="F43" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>15.4</v>
@@ -4024,7 +4026,7 @@
       <c r="K43" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="10" t="n">
         <v>16.4</v>
       </c>
       <c r="M43" s="10" t="n">
@@ -4039,17 +4041,17 @@
       <c r="P43" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q43" s="10" t="n">
-        <v>20.4</v>
+      <c r="Q43" s="3" t="n">
+        <v>30.4</v>
       </c>
       <c r="R43" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>42.6</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>25</v>
@@ -4083,25 +4085,25 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="F44" s="10" t="n">
-        <v>22</v>
+      <c r="F44" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>15.3</v>
@@ -4109,7 +4111,7 @@
       <c r="K44" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="10" t="n">
         <v>18.8</v>
       </c>
       <c r="M44" s="10" t="n">
@@ -4119,13 +4121,13 @@
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>82</v>
+        <v>298.6</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="Q44" s="10" t="n">
-        <v>20.6</v>
+      <c r="Q44" s="3" t="n">
+        <v>30.6</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>21.8</v>
@@ -4168,7 +4170,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D45" s="9" t="n">
         <v>167.8</v>
@@ -4189,7 +4191,7 @@
         <v>33.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>9.4</v>
@@ -4201,10 +4203,10 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>99</v>
+        <v>499</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>21.4</v>
@@ -4216,10 +4218,10 @@
         <v>121</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>115.2</v>
+        <v>116.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>17.9</v>
+        <v>317.9</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>107.1</v>
@@ -4231,7 +4233,7 @@
         <v>115</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>93.5</v>
+        <v>393.6</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>64.40000000000001</v>
@@ -4259,7 +4261,7 @@
       <c r="E46" s="10" t="n">
         <v>17.1</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="9" t="n">
         <v>22.5</v>
       </c>
       <c r="G46" s="3" t="n">
@@ -4275,24 +4277,24 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="L46" s="9" t="n">
+        <v>280.8</v>
+      </c>
+      <c r="L46" s="10" t="n">
         <v>18.3</v>
       </c>
       <c r="M46" s="10" t="n">
         <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>51.1</v>
+        <v>2011</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q46" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q46" s="9" t="n">
         <v>27.5</v>
       </c>
       <c r="R46" s="10" t="n">
@@ -4320,7 +4322,7 @@
         <v>3.6</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>27.8</v>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>28.6</v>
@@ -976,7 +976,7 @@
         <v>22.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>56.3</v>
+        <v>58.3</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>16.8</v>
@@ -1046,7 +1046,7 @@
         <v>19.2</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
@@ -1111,7 +1111,7 @@
         <v>15.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>11.2</v>
@@ -1129,7 +1129,7 @@
         <v>17.4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>31</v>
+        <v>31.8</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>4</v>
@@ -1224,7 +1224,7 @@
         <v>106</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>122.6</v>
+        <v>102.6</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>255.1</v>
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="M10" s="10" t="n">
         <v>16.6</v>
@@ -1325,7 +1325,7 @@
         <v>19.1</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>20</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>13.4</v>
@@ -1425,13 +1425,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>28.2</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>23.1</v>
@@ -1683,7 +1683,7 @@
         <v>17.8</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>11</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>138.8</v>
@@ -1774,7 +1774,7 @@
         <v>49.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>84.2</v>
+        <v>89.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.6</v>
@@ -1876,7 +1876,7 @@
         <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>3.4</v>
@@ -1903,13 +1903,13 @@
         <v>19</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>19.7</v>
+        <v>10.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>120.1</v>
+        <v>22</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>902.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>30.4</v>
@@ -1988,10 +1988,10 @@
         <v>91.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>16.2</v>
+        <v>28.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>58</v>
@@ -2074,7 +2074,7 @@
         <v>19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>28.2</v>
+        <v>54</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16</v>
@@ -2330,7 +2330,7 @@
         <v>76</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="10" t="n">
         <v>145.6</v>
@@ -2460,10 +2460,10 @@
         <v>17</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>25.4</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>3.1</v>
@@ -2478,7 +2478,7 @@
         <v>20.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>18.3</v>
@@ -2490,13 +2490,13 @@
         <v>19.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="10" t="n">
         <v>22.8</v>
@@ -2525,7 +2525,7 @@
         <v>6.8</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>19.6</v>
+        <v>10</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2</v>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="10" t="n">
         <v>27.4</v>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>27.4</v>
@@ -2782,7 +2782,7 @@
         <v>4.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -2827,7 +2827,7 @@
         <v>19.6</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>59.2</v>
+        <v>59.5</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>13.2</v>
@@ -2944,7 +2944,7 @@
         <v>474.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>22</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>20</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="10" t="n">
         <v>26.6</v>
@@ -3063,10 +3063,10 @@
         <v>20.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>59.2</v>
+        <v>59.8</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="V31" s="10" t="n">
         <v>23.6</v>
@@ -3078,7 +3078,7 @@
         <v>19.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>17.2</v>
+        <v>57.2</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>18</v>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>29</v>
+        <v>20.8</v>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="8" t="n">
@@ -3152,10 +3152,10 @@
         <v>44.91</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>9119.1</v>
+        <v>1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>26.2</v>
+        <v>2</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>14.6</v>
@@ -3220,7 +3220,7 @@
         <v>20</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>56</v>
@@ -3339,9 +3339,7 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="10" t="n">
         <v>24.2</v>
       </c>
@@ -3512,7 +3510,7 @@
         <v>132.8</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>882.1</v>
+        <v>88.2</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>11</v>
@@ -3554,7 +3552,7 @@
         <v>102.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>218.8</v>
+        <v>101.7</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>288.6</v>
@@ -3569,7 +3567,7 @@
         <v>95</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>1014.3</v>
+        <v>1.4</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>86</v>
@@ -3626,7 +3624,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>29.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>26.8</v>
@@ -3638,7 +3636,7 @@
         <v>28.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>14.9</v>
@@ -3647,13 +3645,13 @@
         <v>22</v>
       </c>
       <c r="W38" s="9" t="n">
-        <v>11.1</v>
+        <v>5</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>11.1</v>
+        <v>0.1</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>21.8</v>
@@ -3729,7 +3727,7 @@
       <c r="V39" s="8" t="n">
         <v>75.42999999999999</v>
       </c>
-      <c r="W39" s="10" t="n">
+      <c r="W39" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3762,7 +3760,7 @@
         <v>18.4</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>7.8</v>
@@ -3807,12 +3805,12 @@
         <v>57.8</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.4</v>
+        <v>14.4</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W40" s="10" t="n">
+      <c r="W40" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3836,7 +3834,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>25.4</v>
@@ -3854,7 +3852,7 @@
         <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>6</v>
@@ -3887,7 +3885,7 @@
         <v>17.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62.2</v>
+        <v>62.8</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>10.4</v>
@@ -3895,14 +3893,14 @@
       <c r="V41" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W41" s="10" t="n">
+      <c r="W41" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76.2</v>
+        <v>76.5</v>
       </c>
       <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
@@ -3976,7 +3974,7 @@
       <c r="V42" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W42" s="10" t="n">
+      <c r="W42" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4059,8 +4057,8 @@
       <c r="V43" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W43" s="10" t="n">
-        <v>20</v>
+      <c r="W43" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>19.6</v>
@@ -4085,7 +4083,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>30.6</v>
@@ -4100,7 +4098,7 @@
         <v>14.2</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>15.2</v>
+        <v>18.8</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>7.6</v>
@@ -4121,7 +4119,7 @@
         <v>16.4</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>298.6</v>
+        <v>84</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>4</v>
@@ -4144,7 +4142,7 @@
       <c r="V44" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W44" s="10" t="n">
+      <c r="W44" s="3" t="n">
         <v>20</v>
       </c>
       <c r="X44" s="3" t="n">
@@ -4154,7 +4152,7 @@
         <v>14.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4170,7 +4168,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="9" t="n">
         <v>167.8</v>
@@ -4191,7 +4189,7 @@
         <v>33.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>61.2</v>
+        <v>61.5</v>
       </c>
       <c r="K45" s="10" t="n">
         <v>9.4</v>
@@ -4203,7 +4201,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>499</v>
@@ -4230,7 +4228,7 @@
         <v>143</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>115</v>
+        <v>115.8</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>393.6</v>
@@ -4277,7 +4275,7 @@
         <v>10.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>280.8</v>
+        <v>20.8</v>
       </c>
       <c r="L46" s="10" t="n">
         <v>18.3</v>
@@ -4286,13 +4284,13 @@
         <v>16.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>2011</v>
+        <v>200</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>26.2</v>
+        <v>17.5</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>27.5</v>
@@ -4312,7 +4310,7 @@
       <c r="V46" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="9" t="n">
         <v>19</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_multi_day_totals_and_avgs.xlsx
@@ -1199,7 +1199,7 @@
       <c r="J9" s="3" t="n">
         <v>256.4</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>10</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1770,7 +1770,7 @@
       <c r="J16" s="3" t="n">
         <v>50.6</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -2347,7 +2347,7 @@
       <c r="J23" s="3" t="n">
         <v>52.9</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2675,7 +2675,7 @@
       <c r="J27" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="12" t="n"/>
       <c r="L27" s="3" t="n">
         <v>98.8</v>
       </c>
@@ -2920,7 +2920,7 @@
       <c r="J30" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="10" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3491,7 +3491,7 @@
       <c r="J37" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4135,7 +4135,7 @@
       <c r="J45" s="3" t="n">
         <v>61.9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="10" t="n">
         <v>9.4</v>
       </c>
       <c r="L45" s="3" t="n">
